--- a/backend/helpers/dotaciones/resultado_final.xlsx
+++ b/backend/helpers/dotaciones/resultado_final.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Digikal\backend\helpers\dotaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA3B360-00A3-4CD3-84DD-0B6FF1D75FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3B2A22-0498-468B-A02B-90096615E027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Escuelas" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="544">
   <si>
     <t>id</t>
   </si>
@@ -63,1616 +63,1607 @@
     <t>instituto nacional central para varones</t>
   </si>
   <si>
+    <t>instituto nacional de educación diversificada edgar arnoldo medrano</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación básica brenda elizabeth del cid medrano jm</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada maestra sosalina menéndez de medrano</t>
+  </si>
+  <si>
+    <t>escuela nacional de formación secretarial  no.3 jv</t>
+  </si>
+  <si>
+    <t>instituto técnico diversificado para secretariado y oficinista con orientación jurídica y bach. en turismo y hotelería</t>
+  </si>
+  <si>
+    <t xml:space="preserve">escuela normal de educación física </t>
+  </si>
+  <si>
+    <t>instituto normal para señoritas olimpia leal</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada césar augusto martínez barrios</t>
+  </si>
+  <si>
+    <t>instituto normal mixto carlos dubon</t>
+  </si>
+  <si>
+    <t>instituto oficial diversificado con orientación en computación iodoc</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada, ined</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificado</t>
+  </si>
+  <si>
+    <t>escuela nacional de ciencias comerciales mixta nocturna</t>
+  </si>
+  <si>
+    <t>instituto normal para señoritas de oriente</t>
+  </si>
+  <si>
+    <t>escuela de ciencias comerciales nocturna</t>
+  </si>
+  <si>
+    <t>escuela normal bilingüe intercultural/turer aj kanseyaj ch'orti',</t>
+  </si>
+  <si>
+    <t>instituto de bachillerato en computación</t>
+  </si>
+  <si>
+    <t>instituto nacional de eduacicion diverficada</t>
+  </si>
+  <si>
+    <t>escuela nacional mixta nocturna de ciencias comerciales</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada -ined</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada "pilar de valores y conocimientos"</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada "poaquil"</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada "san miguel"</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada"acatenango"</t>
+  </si>
+  <si>
+    <t>instituto técnico industrial para varones de quetzaltenango</t>
+  </si>
+  <si>
+    <t>instituto diversificado adsc. al ineb doctor. werner ovalle lópez</t>
+  </si>
+  <si>
+    <t>escuela nacional de ciencias comerciales sección diurna</t>
+  </si>
+  <si>
+    <t>escuela de artes y oficios femeniles</t>
+  </si>
+  <si>
+    <t>instituto nacional técnico industrial</t>
+  </si>
+  <si>
+    <t>escuela normal bilingue intercultural oxlajuj no'oj</t>
+  </si>
+  <si>
+    <t>escuela normal nacional rural de occidente "guillermo ovando arriola"</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada "2 de junio"</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada "profesor william francisco corado quiñonez"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instituto nacional tecnológico de educación diversificada </t>
+  </si>
+  <si>
+    <t xml:space="preserve">escuela nacional de ciencias comerciales "francisco marroquín" </t>
+  </si>
+  <si>
+    <t>escuela nacional de ciencias comerciales profesor oscar james duque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instituto nacional de educación diversificada </t>
+  </si>
+  <si>
+    <t>instituto normal mixto de occidente, justo rufino barrios, jv.</t>
+  </si>
+  <si>
+    <t>instituto nacional de educación diversificada ined</t>
+  </si>
+  <si>
+    <t>instituto técnico de nivel medio</t>
+  </si>
+  <si>
+    <t>escuela normal bilingüe intercultural mayab' tijob'al oxlajuj tz'i' parcelamiento xalbal.</t>
+  </si>
+  <si>
+    <t>instituto nacional de educacion diversificada</t>
+  </si>
+  <si>
+    <t>instituto nacional de educacion diversificada con orientacion en artes y oficios</t>
+  </si>
+  <si>
+    <t>instituto tecnico diversificado de bachillerato en construccion</t>
+  </si>
+  <si>
+    <t>instituto nacional de administración de empresas</t>
+  </si>
+  <si>
+    <t>instituto normal para varones de oriente</t>
+  </si>
+  <si>
+    <t>instituto tecnologico oficial de la mancomunidad ch'orti'</t>
+  </si>
+  <si>
+    <t>instituto normal centroamericano para varones</t>
+  </si>
+  <si>
+    <t>escuela normal regional de oriente "licenciado clemente marroquin rojas"</t>
+  </si>
+  <si>
+    <t>instituto nacional de educacion diversificada -ined-</t>
+  </si>
+  <si>
+    <t>instituto tecnico de nivel medio</t>
+  </si>
+  <si>
+    <t>instituto tócnico de diversificado bachillerato en contruccion</t>
+  </si>
+  <si>
+    <t>instituto tócnico diversificado de bachillerato en contruccion</t>
+  </si>
+  <si>
     <t>00-01-0619-46</t>
   </si>
   <si>
+    <t>01-06-0009-46</t>
+  </si>
+  <si>
+    <t>01-08-0059-46</t>
+  </si>
+  <si>
+    <t>01-14-0027-46</t>
+  </si>
+  <si>
+    <t>01-06-0115-45</t>
+  </si>
+  <si>
+    <t>01-13-0004-46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-06-0050-46 </t>
+  </si>
+  <si>
+    <t>01-08-1723-46</t>
+  </si>
+  <si>
+    <t>03-02-1004-46</t>
+  </si>
+  <si>
+    <t>03-03-0005-46</t>
+  </si>
+  <si>
+    <t>03-06-0008-46</t>
+  </si>
+  <si>
+    <t>03-01-1231-46</t>
+  </si>
+  <si>
+    <t>03-01-0058-46</t>
+  </si>
+  <si>
+    <t>07-10-0047-46</t>
+  </si>
+  <si>
+    <t>07-10-0048-46</t>
+  </si>
+  <si>
+    <t>07-10-0007-46</t>
+  </si>
+  <si>
+    <t>07-06-0036-46</t>
+  </si>
+  <si>
+    <t>07-19-0103-46</t>
+  </si>
+  <si>
+    <t>07-04-0023-46</t>
+  </si>
+  <si>
+    <t>11-03-0020-46</t>
+  </si>
+  <si>
+    <t>11-04-0011-46</t>
+  </si>
+  <si>
+    <t>11-01-0081-46</t>
+  </si>
+  <si>
+    <t>11-09-0026-46</t>
+  </si>
+  <si>
+    <t>11-02-0015-46</t>
+  </si>
+  <si>
+    <t>11-01-0076-46</t>
+  </si>
+  <si>
+    <t>19-07-0004-46</t>
+  </si>
+  <si>
+    <t>19-02-0001-46</t>
+  </si>
+  <si>
+    <t>19-01-0116-46</t>
+  </si>
+  <si>
+    <t>19-01-0079-46</t>
+  </si>
+  <si>
+    <t>20-01-0034-46</t>
+  </si>
+  <si>
+    <t>20-01-0024-46</t>
+  </si>
+  <si>
+    <t>20-05-1847-46</t>
+  </si>
+  <si>
+    <t>20-09-1794-46</t>
+  </si>
+  <si>
+    <t>05-03-0009-46</t>
+  </si>
+  <si>
+    <t>05-07-0024-46</t>
+  </si>
+  <si>
+    <t>05-01-0146-46</t>
+  </si>
+  <si>
+    <t>05-04-0017-46</t>
+  </si>
+  <si>
+    <t>17-14-0034-46</t>
+  </si>
+  <si>
+    <t>17-03-0124-46</t>
+  </si>
+  <si>
+    <t>17-05-0168-46</t>
+  </si>
+  <si>
+    <t>17-05-0167-46</t>
+  </si>
+  <si>
+    <t>04-15-0008-46</t>
+  </si>
+  <si>
+    <t>04-02-0009-46</t>
+  </si>
+  <si>
+    <t>04-08-0008-46</t>
+  </si>
+  <si>
+    <t>04-11-0002-46</t>
+  </si>
+  <si>
+    <t>09-01-0825-46</t>
+  </si>
+  <si>
+    <t>09-01-0826-46</t>
+  </si>
+  <si>
+    <t>09-19-0013-46</t>
+  </si>
+  <si>
+    <t>09-01-0155-46</t>
+  </si>
+  <si>
+    <t>09-01-1384-46</t>
+  </si>
+  <si>
+    <t>09-04-0880-46</t>
+  </si>
+  <si>
+    <t>15-03-0076-46</t>
+  </si>
+  <si>
+    <t>16-12-0189-46</t>
+  </si>
+  <si>
+    <t>16-01-0616-46</t>
+  </si>
+  <si>
+    <t>16-10-0064-46</t>
+  </si>
+  <si>
+    <t>08-01-0106-46</t>
+  </si>
+  <si>
+    <t>08-03-0055-46</t>
+  </si>
+  <si>
+    <t>08-08-0020-46</t>
+  </si>
+  <si>
+    <t>08-01-2234-46</t>
+  </si>
+  <si>
+    <t>22-01-0298-46</t>
+  </si>
+  <si>
+    <t>22-01-0374-46</t>
+  </si>
+  <si>
+    <t>22-09-0014-46</t>
+  </si>
+  <si>
+    <t>22-04-0023-46</t>
+  </si>
+  <si>
+    <t>02-03-0022-46</t>
+  </si>
+  <si>
+    <t>02-05-0018-46</t>
+  </si>
+  <si>
+    <t>02-03-0112-46</t>
+  </si>
+  <si>
+    <t>02-07-0009-46</t>
+  </si>
+  <si>
+    <t>18-04-0373-46</t>
+  </si>
+  <si>
+    <t>18-01-0174-46</t>
+  </si>
+  <si>
+    <t>18-04-0087-46</t>
+  </si>
+  <si>
+    <t>18-05-0482-46</t>
+  </si>
+  <si>
+    <t>12-19-0048-46</t>
+  </si>
+  <si>
+    <t>12-01-0048-46</t>
+  </si>
+  <si>
+    <t>12-16-0027-46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-03-0018-46 </t>
+  </si>
+  <si>
+    <t>06-09-0027-46</t>
+  </si>
+  <si>
+    <t>06-01-0069-46</t>
+  </si>
+  <si>
+    <t>06-10-0022-46</t>
+  </si>
+  <si>
+    <t>10-03-0012-46</t>
+  </si>
+  <si>
+    <t>10-18-0006-46</t>
+  </si>
+  <si>
+    <t>10-09-0009-46</t>
+  </si>
+  <si>
+    <t>10-06-0016-46</t>
+  </si>
+  <si>
+    <t>14-14-0024-46</t>
+  </si>
+  <si>
+    <t>14-03-0027-46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-01-6123-46 </t>
+  </si>
+  <si>
+    <t>14-20-0147-46</t>
+  </si>
+  <si>
+    <t>13-31-0019-46</t>
+  </si>
+  <si>
+    <t>13-01-0421-46</t>
+  </si>
+  <si>
+    <t>13-17-0075-46</t>
+  </si>
+  <si>
+    <t>16-14-0054-46</t>
+  </si>
+  <si>
+    <t>16-01-0428-46</t>
+  </si>
+  <si>
+    <t>16-11-0027-46</t>
+  </si>
+  <si>
+    <t>16-16-0049-46</t>
+  </si>
+  <si>
+    <t>16-07-0117-46</t>
+  </si>
+  <si>
+    <t>16-03-0087-46</t>
+  </si>
+  <si>
+    <t>16-06-0090-46</t>
+  </si>
+  <si>
+    <t>16-09-0386-46</t>
+  </si>
+  <si>
+    <t>16-09-0720-46</t>
+  </si>
+  <si>
+    <t>16-09-0830-46</t>
+  </si>
+  <si>
+    <t>16-02-0013-46</t>
+  </si>
+  <si>
+    <t>16-05-0017-46</t>
+  </si>
+  <si>
+    <t>15-08-0200-46</t>
+  </si>
+  <si>
+    <t>15-08-0207-46</t>
+  </si>
+  <si>
+    <t>15-08-0219-46</t>
+  </si>
+  <si>
+    <t>15-03-0046-46</t>
+  </si>
+  <si>
+    <t>15-03-0085-46</t>
+  </si>
+  <si>
+    <t>15-01-0087-46</t>
+  </si>
+  <si>
+    <t>15-01-0116-46</t>
+  </si>
+  <si>
+    <t>15-01-1274-46</t>
+  </si>
+  <si>
+    <t>15-07-0036-46</t>
+  </si>
+  <si>
+    <t>15-02-0023-46</t>
+  </si>
+  <si>
+    <t>15-02-0058-46</t>
+  </si>
+  <si>
+    <t>15-02-0094-46</t>
+  </si>
+  <si>
+    <t>15-02-0111-46</t>
+  </si>
+  <si>
+    <t>15-02-0125-46</t>
+  </si>
+  <si>
+    <t>15-02-0126-46</t>
+  </si>
+  <si>
+    <t>15-06-0006-46</t>
+  </si>
+  <si>
+    <t>20-01-0036-46</t>
+  </si>
+  <si>
+    <t>20-08-0006-46</t>
+  </si>
+  <si>
+    <t>20-04-0097-46</t>
+  </si>
+  <si>
+    <t>20-10-0013-46</t>
+  </si>
+  <si>
+    <t>13-27-0076-46</t>
+  </si>
+  <si>
+    <t>13-01-0112-46</t>
+  </si>
+  <si>
+    <t>13-01-0323-46</t>
+  </si>
+  <si>
+    <t>13-07-0067-46</t>
+  </si>
+  <si>
+    <t>13-32-0035-46</t>
+  </si>
+  <si>
+    <t>21-01-0104-46</t>
+  </si>
+  <si>
+    <t>21-01-0391-46</t>
+  </si>
+  <si>
+    <t>21-07-0063-46</t>
+  </si>
+  <si>
+    <t>21-06-0021-46</t>
+  </si>
+  <si>
+    <t>21-06-0239-46</t>
+  </si>
+  <si>
+    <t>21-05-0017-46</t>
+  </si>
+  <si>
+    <t>21-03-0010-46</t>
+  </si>
+  <si>
+    <t>21-03-0034-46</t>
+  </si>
+  <si>
+    <t>21-02-0050-46</t>
+  </si>
+  <si>
+    <t>14-19-0055-46</t>
+  </si>
+  <si>
+    <t>14-10-0059-46</t>
+  </si>
+  <si>
+    <t>14-13-0068-46</t>
+  </si>
+  <si>
+    <t>14-15-0103-46</t>
+  </si>
+  <si>
+    <t>14-01-0112-46</t>
+  </si>
+  <si>
+    <t>14-01-0236-46</t>
+  </si>
+  <si>
+    <t>14-06-0020-46</t>
+  </si>
+  <si>
+    <t>15-06-0009-46</t>
+  </si>
+  <si>
     <t>guatemala</t>
   </si>
   <si>
+    <t xml:space="preserve">guatemala </t>
+  </si>
+  <si>
+    <t>sacatepéquez</t>
+  </si>
+  <si>
+    <t>sololá</t>
+  </si>
+  <si>
+    <t>retalhuleu</t>
+  </si>
+  <si>
+    <t>zacapa</t>
+  </si>
+  <si>
+    <t>chiquimula</t>
+  </si>
+  <si>
+    <t>escuintla</t>
+  </si>
+  <si>
+    <t>petén</t>
+  </si>
+  <si>
+    <t>chimaltenango</t>
+  </si>
+  <si>
+    <t>quetzaltenango</t>
+  </si>
+  <si>
+    <t>baja verapaz</t>
+  </si>
+  <si>
+    <t>alta verapaz</t>
+  </si>
+  <si>
+    <t>totonicapán</t>
+  </si>
+  <si>
+    <t>jutiapa</t>
+  </si>
+  <si>
+    <t>el progreso</t>
+  </si>
+  <si>
+    <t>izabal</t>
+  </si>
+  <si>
+    <t>san marcos</t>
+  </si>
+  <si>
+    <t>santa rosa</t>
+  </si>
+  <si>
+    <t>suchitepéquez</t>
+  </si>
+  <si>
+    <t>quiché</t>
+  </si>
+  <si>
+    <t>huehuetenango</t>
+  </si>
+  <si>
+    <t>jalapa</t>
+  </si>
+  <si>
+    <t>chinautla</t>
+  </si>
+  <si>
+    <t>mixco</t>
+  </si>
+  <si>
+    <t>amatitlán</t>
+  </si>
+  <si>
+    <t>fraijanes</t>
+  </si>
+  <si>
+    <t>jocotenango</t>
+  </si>
+  <si>
+    <t>pastores</t>
+  </si>
+  <si>
+    <t>santiago sacatepéquez</t>
+  </si>
+  <si>
+    <t>antigua guatemala</t>
+  </si>
+  <si>
+    <t>panajachel</t>
+  </si>
+  <si>
+    <t>santa catarina ixtahuacán</t>
+  </si>
+  <si>
+    <t>santiago atitlán</t>
+  </si>
+  <si>
+    <t>santa lucía utatlán</t>
+  </si>
+  <si>
+    <t>santa cruz muluá</t>
+  </si>
+  <si>
+    <t>san martín zapotitlán</t>
+  </si>
+  <si>
+    <t>el asintal</t>
+  </si>
+  <si>
+    <t>san sebastián</t>
+  </si>
+  <si>
+    <t>cabañas</t>
+  </si>
+  <si>
+    <t>estanzuela</t>
+  </si>
+  <si>
+    <t>camotán</t>
+  </si>
+  <si>
+    <t>quezaltepeque</t>
+  </si>
+  <si>
+    <t>la democracia</t>
+  </si>
+  <si>
+    <t>la gomera</t>
+  </si>
+  <si>
+    <t>siquinalá</t>
+  </si>
+  <si>
+    <t>el chal</t>
+  </si>
+  <si>
+    <t>san benito</t>
+  </si>
+  <si>
+    <t>la libertad</t>
+  </si>
+  <si>
+    <t>zaragoza</t>
+  </si>
+  <si>
+    <t>san josé poaquil</t>
+  </si>
+  <si>
+    <t>san miguel pochuta</t>
+  </si>
+  <si>
+    <t>acatenango</t>
+  </si>
+  <si>
+    <t>el palmar</t>
+  </si>
+  <si>
+    <t>san carlos sija</t>
+  </si>
+  <si>
+    <t>rabinal</t>
+  </si>
+  <si>
+    <t>santa maría cahabón</t>
+  </si>
+  <si>
+    <t>cobán</t>
+  </si>
+  <si>
+    <t>san juan chamelco</t>
+  </si>
+  <si>
+    <t>san francisco el alto</t>
+  </si>
+  <si>
+    <t>el adelanto</t>
+  </si>
+  <si>
+    <t>agua blanca</t>
+  </si>
+  <si>
+    <t>san agustín acasaguastlán</t>
+  </si>
+  <si>
+    <t>el jícaro</t>
+  </si>
+  <si>
+    <t>sanarate</t>
+  </si>
+  <si>
+    <t>morales</t>
+  </si>
+  <si>
+    <t>puerto barrios</t>
+  </si>
+  <si>
+    <t>los amates</t>
+  </si>
+  <si>
+    <t>san pablo</t>
+  </si>
+  <si>
+    <t>catarina</t>
+  </si>
+  <si>
+    <t>san antonio sacatepéquez</t>
+  </si>
+  <si>
+    <t>taxisco</t>
+  </si>
+  <si>
+    <t>cuilapa</t>
+  </si>
+  <si>
+    <t>santa maría ixhuatán</t>
+  </si>
+  <si>
+    <t>san francisco zapotitlán</t>
+  </si>
+  <si>
+    <t>zunilito</t>
+  </si>
+  <si>
+    <t>santo domingo suchitepéquez</t>
+  </si>
+  <si>
+    <t>san andrés sajcabajá</t>
+  </si>
+  <si>
+    <t>chinique</t>
+  </si>
+  <si>
+    <t>santa cruz del quiché</t>
+  </si>
+  <si>
+    <t>ixcán</t>
+  </si>
+  <si>
+    <t>santa ana huista</t>
+  </si>
+  <si>
+    <t>santa eulalia</t>
+  </si>
+  <si>
+    <t>chahal</t>
+  </si>
+  <si>
+    <t>lanquín</t>
+  </si>
+  <si>
+    <t>panzós</t>
+  </si>
+  <si>
+    <t>san cristóbal verapaz</t>
+  </si>
+  <si>
+    <t>san pedro carchá</t>
+  </si>
+  <si>
+    <t>santa cruz verapaz</t>
+  </si>
+  <si>
+    <t>tamahú</t>
+  </si>
+  <si>
+    <t>purulhá</t>
+  </si>
+  <si>
+    <t>salamá</t>
+  </si>
+  <si>
+    <t>san jerónimo</t>
+  </si>
+  <si>
+    <t>san miguel chicaj</t>
+  </si>
+  <si>
+    <t>santa cruz el chol</t>
+  </si>
+  <si>
+    <t>concepción las minas</t>
+  </si>
+  <si>
+    <t>san jacinto</t>
+  </si>
+  <si>
+    <t>aguacatán</t>
+  </si>
+  <si>
+    <t>jacaltenango</t>
+  </si>
+  <si>
+    <t>unión cantinil</t>
+  </si>
+  <si>
+    <t>mataquescuintla</t>
+  </si>
+  <si>
+    <t>monjas</t>
+  </si>
+  <si>
+    <t>san carlos alzatate</t>
+  </si>
+  <si>
+    <t>san luis jilotepeque</t>
+  </si>
+  <si>
+    <t>san pedro pinula</t>
+  </si>
+  <si>
+    <t>chicamán</t>
+  </si>
+  <si>
+    <t>cunén</t>
+  </si>
+  <si>
+    <t>nebaj</t>
+  </si>
+  <si>
+    <t>chichicastenango</t>
+  </si>
+  <si>
     <t>9° avenida 9-27 zona 1</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada edgar arnoldo medrano</t>
-  </si>
-  <si>
-    <t>01-06-0009-46</t>
-  </si>
-  <si>
-    <t>chinautla</t>
-  </si>
-  <si>
     <t>lote 0 sector 43 tierra nueva i</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada</t>
-  </si>
-  <si>
-    <t>01-08-0059-46</t>
-  </si>
-  <si>
-    <t>mixco</t>
-  </si>
-  <si>
     <t>8° av. 18-58 colonia primero de julio zona 5 de mixco</t>
   </si>
   <si>
-    <t>01-14-0027-46</t>
-  </si>
-  <si>
-    <t>amatitlán</t>
-  </si>
-  <si>
     <t>7 calle final 1-45 colonia villas del río amatitlán</t>
   </si>
   <si>
-    <t>instituto nacional de educación básica brenda elizabeth del cid medrano jm</t>
-  </si>
-  <si>
-    <t>01-06-0115-45</t>
-  </si>
-  <si>
     <t>avenida belice 1-00 segundo nivel mercado santa lucia</t>
   </si>
   <si>
-    <t>01-13-0004-46</t>
-  </si>
-  <si>
-    <t>fraijanes</t>
-  </si>
-  <si>
     <t xml:space="preserve">5ta. calle 4-90 zona 1, fraijanes </t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada maestra sosalina menéndez de medrano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01-06-0050-46 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">chinautla </t>
-  </si>
-  <si>
     <t xml:space="preserve">lote 95a callejon 18 calle principal,  aldea el durazno chinautla. </t>
   </si>
   <si>
-    <t>escuela nacional de formación secretarial  no.3 jv</t>
-  </si>
-  <si>
-    <t>01-08-1723-46</t>
-  </si>
-  <si>
     <t>10a. ave. 10a. calle zona 3 de mixco colonia nueva montserrat</t>
   </si>
   <si>
-    <t>instituto técnico diversificado para secretariado y oficinista con orientación jurídica y bach. en turismo y hotelería</t>
-  </si>
-  <si>
-    <t>03-02-1004-46</t>
-  </si>
-  <si>
-    <t>jocotenango</t>
-  </si>
-  <si>
     <t>1a. avenida y 1a. calle zona 3</t>
   </si>
   <si>
-    <t>03-03-0005-46</t>
-  </si>
-  <si>
-    <t>pastores</t>
-  </si>
-  <si>
     <t>calle real</t>
   </si>
   <si>
-    <t>03-06-0008-46</t>
-  </si>
-  <si>
-    <t>santiago sacatepéquez</t>
-  </si>
-  <si>
     <t>3ra. avenida y 4ta. calle, zona 4</t>
   </si>
   <si>
-    <t xml:space="preserve">escuela normal de educación física </t>
-  </si>
-  <si>
-    <t>03-01-1231-46</t>
-  </si>
-  <si>
-    <t>sacatepéquez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">antigua guatemala </t>
-  </si>
-  <si>
     <t xml:space="preserve">kilómetro 2 salida a santa maría de jesús finca primavera </t>
   </si>
   <si>
-    <t>instituto normal para señoritas olimpia leal</t>
-  </si>
-  <si>
-    <t>03-01-0058-46</t>
-  </si>
-  <si>
-    <t>antigua guatemala</t>
-  </si>
-  <si>
     <t>5a.calle oriente n-15</t>
   </si>
   <si>
-    <t>07-10-0047-46</t>
-  </si>
-  <si>
-    <t>sololá</t>
-  </si>
-  <si>
-    <t>panajachel</t>
-  </si>
-  <si>
     <t>aldea patanatic</t>
   </si>
   <si>
-    <t>07-10-0048-46</t>
-  </si>
-  <si>
     <t>barrio jucanya</t>
   </si>
   <si>
-    <t>07-10-0007-46</t>
-  </si>
-  <si>
     <t>canton tzala</t>
   </si>
   <si>
-    <t>07-06-0036-46</t>
-  </si>
-  <si>
     <t>baarrio el calvario</t>
   </si>
   <si>
-    <t>07-19-0103-46</t>
-  </si>
-  <si>
     <t>canton tzanchali, aldea cerro de oro</t>
   </si>
   <si>
-    <t>07-04-0023-46</t>
-  </si>
-  <si>
-    <t>santa lucía utatlán</t>
-  </si>
-  <si>
     <t>cabecera municipal de santa lucía utatlán</t>
   </si>
   <si>
-    <t>11-03-0020-46</t>
-  </si>
-  <si>
-    <t>retalhuleu</t>
-  </si>
-  <si>
     <t>edificio la rreforma en 1a. avenida 100, zona 2</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada césar augusto martínez barrios</t>
-  </si>
-  <si>
-    <t>11-04-0011-46</t>
-  </si>
-  <si>
     <t>cabecera municipal</t>
   </si>
   <si>
-    <t>instituto normal mixto carlos dubon</t>
-  </si>
-  <si>
-    <t>11-01-0081-46</t>
-  </si>
-  <si>
     <t>3a calle 6-49 zona 4</t>
   </si>
   <si>
-    <t>11-09-0026-46</t>
-  </si>
-  <si>
-    <t>el asintal</t>
-  </si>
-  <si>
     <t>aldea sibana</t>
   </si>
   <si>
-    <t>11-02-0015-46</t>
-  </si>
-  <si>
-    <t>san sebastián</t>
-  </si>
-  <si>
     <t>avenida central caserío samala 1.</t>
   </si>
   <si>
-    <t>instituto oficial diversificado con orientación en computación iodoc</t>
-  </si>
-  <si>
-    <t>11-01-0076-46</t>
-  </si>
-  <si>
     <t>1a ave. 4-08 zona 2</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada, ined</t>
-  </si>
-  <si>
-    <t>19-07-0004-46</t>
-  </si>
-  <si>
-    <t>zacapa</t>
-  </si>
-  <si>
-    <t>cabañas</t>
-  </si>
-  <si>
     <t>1ra calle 05-69 zona 4, barrio san pedro cabañas</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificado</t>
-  </si>
-  <si>
-    <t>19-02-0001-46</t>
-  </si>
-  <si>
-    <t>estanzuela</t>
-  </si>
-  <si>
     <t>barrio la laguna i</t>
   </si>
   <si>
-    <t>19-01-0116-46</t>
-  </si>
-  <si>
     <t>7a. avenida "a" final y 9a. calle zona 2 barrio la reforma</t>
   </si>
   <si>
-    <t>escuela nacional de ciencias comerciales mixta nocturna</t>
-  </si>
-  <si>
-    <t>19-01-0079-46</t>
-  </si>
-  <si>
     <t>4a. calle 16-10 zona 1. barrio el calvario</t>
   </si>
   <si>
-    <t>instituto normal para señoritas de oriente</t>
-  </si>
-  <si>
-    <t>20-01-0034-46</t>
-  </si>
-  <si>
-    <t>chiquimula</t>
-  </si>
-  <si>
     <t>4a. calle 6-00 zona 1</t>
   </si>
   <si>
-    <t>escuela de ciencias comerciales nocturna</t>
-  </si>
-  <si>
-    <t>20-01-0024-46</t>
-  </si>
-  <si>
     <t>10a. avenida 3-71 zona 1</t>
   </si>
   <si>
-    <t>escuela normal bilingüe intercultural/turer aj kanseyaj ch'orti',</t>
-  </si>
-  <si>
-    <t>20-05-1847-46</t>
-  </si>
-  <si>
-    <t>camotán</t>
-  </si>
-  <si>
     <t>barrio el cementerio, camotán, chiquimula</t>
   </si>
   <si>
-    <t>instituto de bachillerato en computación</t>
-  </si>
-  <si>
-    <t>20-09-1794-46</t>
-  </si>
-  <si>
-    <t>quezaltepeque</t>
-  </si>
-  <si>
     <t>3ra. avenida 1-68 zona 1</t>
   </si>
   <si>
-    <t>instituto nacional de eduacicion diverficada</t>
-  </si>
-  <si>
-    <t>05-03-0009-46</t>
-  </si>
-  <si>
-    <t>escuintla</t>
-  </si>
-  <si>
-    <t>democracia</t>
-  </si>
-  <si>
     <t>frente a 2a. avenida de colonia san vicente la campiña</t>
   </si>
   <si>
-    <t>05-07-0024-46</t>
-  </si>
-  <si>
-    <t>la gomera</t>
-  </si>
-  <si>
     <t>1ra. avenida, lote 2-40 colonia 15 de septiembre</t>
   </si>
   <si>
-    <t>escuela nacional mixta nocturna de ciencias comerciales</t>
-  </si>
-  <si>
-    <t>05-01-0146-46</t>
-  </si>
-  <si>
     <t>7a calle 3-02 zona 1 escuintla</t>
   </si>
   <si>
-    <t>05-04-0017-46</t>
-  </si>
-  <si>
-    <t>siquinalá</t>
-  </si>
-  <si>
     <t>3a calle 3-95 colonia tierra verde</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada -ined</t>
-  </si>
-  <si>
-    <t>17-14-0034-46</t>
-  </si>
-  <si>
-    <t>petén</t>
-  </si>
-  <si>
     <t>barrio el milagro el chal, petén</t>
   </si>
   <si>
-    <t>17-03-0124-46</t>
-  </si>
-  <si>
-    <t>san benito</t>
-  </si>
-  <si>
     <t>barrio valle nuevo, san benito, petén</t>
   </si>
   <si>
-    <t>17-05-0168-46</t>
-  </si>
-  <si>
-    <t>la libertad</t>
-  </si>
-  <si>
     <t>nueva lotificación</t>
   </si>
   <si>
-    <t>17-05-0167-46</t>
-  </si>
-  <si>
     <t>aldea el naranjo</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada "pilar de valores y conocimientos"</t>
-  </si>
-  <si>
-    <t>04-15-0008-46</t>
-  </si>
-  <si>
-    <t>chimaltenango</t>
-  </si>
-  <si>
-    <t>zaragoza</t>
-  </si>
-  <si>
     <t>2da. avenida 1-13 zona 2</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada "poaquil"</t>
-  </si>
-  <si>
-    <t>04-02-0009-46</t>
-  </si>
-  <si>
-    <t>san josé poaquil</t>
-  </si>
-  <si>
     <t>calle principal zona 2</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada "san miguel"</t>
-  </si>
-  <si>
-    <t>04-08-0008-46</t>
-  </si>
-  <si>
-    <t>san miguel pochuta</t>
-  </si>
-  <si>
     <t>1ra. avenida 6-57, zona 1</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada"acatenango"</t>
-  </si>
-  <si>
-    <t>04-11-0002-46</t>
-  </si>
-  <si>
-    <t>acatenango</t>
-  </si>
-  <si>
     <t>colonia potreritos</t>
   </si>
   <si>
-    <t>instituto técnico industrial para varones de quetzaltenango</t>
-  </si>
-  <si>
-    <t>09-01-0825-46</t>
-  </si>
-  <si>
     <t>36 avenida y 0 calle, barrio garibaldi zona 8 quetzaltenango</t>
   </si>
   <si>
-    <t>instituto diversificado adsc. al ineb doctor. werner ovalle lópez</t>
-  </si>
-  <si>
-    <t>09-01-0826-46</t>
-  </si>
-  <si>
     <t>25 av. entre 4ta y 7ma calle zona 3</t>
   </si>
   <si>
-    <t>09-19-0013-46</t>
-  </si>
-  <si>
-    <t>quetzaltenango</t>
-  </si>
-  <si>
-    <t>el palmar</t>
-  </si>
-  <si>
     <t>5a. av. 6-63 zona 1, el palmar, quetzaltenango</t>
   </si>
   <si>
-    <t>escuela nacional de ciencias comerciales sección diurna</t>
-  </si>
-  <si>
-    <t>09-01-0155-46</t>
-  </si>
-  <si>
     <t>5ta. calle 12-60 zona 3 quetzaltenango</t>
   </si>
   <si>
-    <t>escuela de artes y oficios femeniles</t>
-  </si>
-  <si>
-    <t>09-01-1384-46</t>
-  </si>
-  <si>
     <t xml:space="preserve">14 avenida a-20 zona 1 quetzaltenango </t>
   </si>
   <si>
-    <t>instituto nacional técnico industrial</t>
-  </si>
-  <si>
-    <t>09-04-0880-46</t>
-  </si>
-  <si>
-    <t>san carlos sija</t>
-  </si>
-  <si>
     <t xml:space="preserve">2a. av. 5-28 zona 1 </t>
   </si>
   <si>
-    <t>escuela normal bilingue intercultural oxlajuj no'oj</t>
-  </si>
-  <si>
-    <t>15-03-0076-46</t>
-  </si>
-  <si>
-    <t>baja verapaz</t>
-  </si>
-  <si>
-    <t>rabinal</t>
-  </si>
-  <si>
     <t>aldea pachulum</t>
   </si>
   <si>
-    <t>16-12-0189-46</t>
-  </si>
-  <si>
-    <t>alta verapaz</t>
-  </si>
-  <si>
-    <t>santa maria cahabon</t>
-  </si>
-  <si>
     <t>aldea pinares</t>
   </si>
   <si>
-    <t>16-01-0616-46</t>
-  </si>
-  <si>
-    <t>coban</t>
-  </si>
-  <si>
     <t>aldea salacuim</t>
   </si>
   <si>
-    <t>16-10-0064-46</t>
-  </si>
-  <si>
-    <t>san juan chamelco</t>
-  </si>
-  <si>
     <t>2da. avenida 7-66 zona 2, barrio santa ana oriental</t>
   </si>
   <si>
-    <t>escuela normal nacional rural de occidente "guillermo ovando arriola"</t>
-  </si>
-  <si>
-    <t>08-01-0106-46</t>
-  </si>
-  <si>
-    <t>totonicapán</t>
-  </si>
-  <si>
     <t>zona 5 paraje parramon</t>
   </si>
   <si>
-    <t>08-03-0055-46</t>
-  </si>
-  <si>
-    <t>san francisco el alto</t>
-  </si>
-  <si>
     <t>parajere chiventur, aldea chivarreto</t>
   </si>
   <si>
-    <t>08-08-0020-46</t>
-  </si>
-  <si>
-    <t>san bartolo agua calientes</t>
-  </si>
-  <si>
     <t>zona 4, colonia los cipreses, san bartolo aguas calientes</t>
   </si>
   <si>
-    <t>08-01-2234-46</t>
-  </si>
-  <si>
     <t>17 avenida 2-250 zona 2, totonicapán</t>
   </si>
   <si>
-    <t>22-01-0298-46</t>
-  </si>
-  <si>
-    <t>jutiapa</t>
-  </si>
-  <si>
     <t>aldea los anonos, cantón valencia</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada "2 de junio"</t>
-  </si>
-  <si>
-    <t>22-01-0374-46</t>
-  </si>
-  <si>
     <t>complejo educativo, bario el condor</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada "profesor william francisco corado quiñonez"</t>
-  </si>
-  <si>
-    <t>22-09-0014-46</t>
-  </si>
-  <si>
-    <t>el adelanto</t>
-  </si>
-  <si>
     <t>barrio sitio arriba</t>
   </si>
   <si>
-    <t>22-04-0023-46</t>
-  </si>
-  <si>
-    <t>agua blanca</t>
-  </si>
-  <si>
     <t>barrio tecuan</t>
   </si>
   <si>
-    <t>02-03-0022-46</t>
-  </si>
-  <si>
-    <t>el progreso</t>
-  </si>
-  <si>
-    <t>san agustín acasaguastlán</t>
-  </si>
-  <si>
     <t>barrio la escuela, aldea el rancho.</t>
   </si>
   <si>
-    <t xml:space="preserve">instituto nacional tecnológico de educación diversificada </t>
-  </si>
-  <si>
-    <t>02-05-0018-46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">el jícaro </t>
-  </si>
-  <si>
     <t>barrio buenos aires</t>
   </si>
   <si>
-    <t>02-03-0112-46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">san agustín acasaguastlán </t>
-  </si>
-  <si>
     <t>aldea el morro</t>
   </si>
   <si>
-    <t>02-07-0009-46</t>
-  </si>
-  <si>
-    <t>sanarate</t>
-  </si>
-  <si>
     <t xml:space="preserve">zona 4, colindante con polideportivo, campo de caminos </t>
   </si>
   <si>
-    <t xml:space="preserve">escuela nacional de ciencias comerciales "francisco marroquín" </t>
-  </si>
-  <si>
-    <t>18-04-0373-46</t>
-  </si>
-  <si>
-    <t>izabal</t>
-  </si>
-  <si>
-    <t>morales</t>
-  </si>
-  <si>
     <t>avenida vicente cozza</t>
   </si>
   <si>
-    <t>18-01-0174-46</t>
-  </si>
-  <si>
-    <t>puerto barrios</t>
-  </si>
-  <si>
     <t>colonia maria luisa 1 aldea santo tomás de castilla, ubicado en escuela juan josé orezco posadas</t>
   </si>
   <si>
-    <t>18-04-0087-46</t>
-  </si>
-  <si>
-    <t>escuela nacional de ciencias comerciales profesor oscar james duque</t>
-  </si>
-  <si>
-    <t>18-05-0482-46</t>
-  </si>
-  <si>
-    <t>los amates</t>
-  </si>
-  <si>
     <t>colonia santa marta, barrio el pozón</t>
   </si>
   <si>
-    <t xml:space="preserve">instituto nacional de educación diversificada </t>
-  </si>
-  <si>
-    <t>12-19-0048-46</t>
-  </si>
-  <si>
-    <t>san marcos</t>
-  </si>
-  <si>
-    <t>san pablo</t>
-  </si>
-  <si>
-    <t>instituto normal mixto de occidente, justo rufino barrios, jv.</t>
-  </si>
-  <si>
-    <t>12-01-0048-46</t>
-  </si>
-  <si>
     <t>10a. avenida 8-27 zona 3</t>
   </si>
   <si>
-    <t>12-16-0027-46</t>
-  </si>
-  <si>
-    <t>catarina</t>
-  </si>
-  <si>
     <t>aldea el sitio</t>
   </si>
   <si>
-    <t xml:space="preserve">12-03-0018-46 </t>
-  </si>
-  <si>
-    <t>san antonio sacatepéquez</t>
-  </si>
-  <si>
-    <t>06-09-0027-46</t>
-  </si>
-  <si>
-    <t>santa rosa</t>
-  </si>
-  <si>
-    <t>taxisco</t>
-  </si>
-  <si>
     <t>aldea candelaria</t>
   </si>
   <si>
-    <t>06-01-0069-46</t>
-  </si>
-  <si>
-    <t>cuilapa</t>
-  </si>
-  <si>
     <t>lotificación bella vista, barrio el calvario</t>
   </si>
   <si>
-    <t>06-10-0022-46</t>
-  </si>
-  <si>
-    <t>santa maría ixhuatán</t>
-  </si>
-  <si>
     <t>cantón buena vista</t>
   </si>
   <si>
-    <t>10-03-0012-46</t>
-  </si>
-  <si>
-    <t>suchitepéquez</t>
-  </si>
-  <si>
-    <t>san francisco zapotitlan</t>
-  </si>
-  <si>
     <t xml:space="preserve"> colonia el rosario</t>
   </si>
   <si>
-    <t>10-18-0006-46</t>
-  </si>
-  <si>
-    <t>zunulito</t>
-  </si>
-  <si>
     <t>2da. avenida 3-10 zona 1</t>
   </si>
   <si>
-    <t>10-09-0009-46</t>
-  </si>
-  <si>
-    <t>san pablo jopilas</t>
-  </si>
-  <si>
     <t xml:space="preserve">calle principal </t>
   </si>
   <si>
-    <t>10-06-0016-46</t>
-  </si>
-  <si>
-    <t>santo domingo suchitepéquez</t>
-  </si>
-  <si>
     <t>1 avenida 5-15 zona 1 cantón el calvario santo domingo, suchitepéquez</t>
   </si>
   <si>
-    <t>14-14-0024-46</t>
-  </si>
-  <si>
-    <t>quiché</t>
-  </si>
-  <si>
-    <t>san andrés sajcabajá</t>
-  </si>
-  <si>
     <t>7a. avenida 3-211 zona 4</t>
   </si>
   <si>
-    <t>instituto nacional de educación diversificada ined</t>
-  </si>
-  <si>
-    <t>14-03-0027-46</t>
-  </si>
-  <si>
-    <t>chinique</t>
-  </si>
-  <si>
     <t xml:space="preserve">aldea agua tibia i, chinique, quiché. </t>
   </si>
   <si>
-    <t>instituto técnico de nivel medio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14-01-6123-46 </t>
-  </si>
-  <si>
-    <t>santa cruz del quiché</t>
-  </si>
-  <si>
     <t>final de la zona 4 colonia celajes</t>
   </si>
   <si>
-    <t>escuela normal bilingüe intercultural mayab' tijob'al oxlajuj tz'i' parcelamiento xalbal.</t>
-  </si>
-  <si>
-    <t>14-20-0147-46</t>
-  </si>
-  <si>
-    <t>ixcán</t>
-  </si>
-  <si>
     <t>parcelamiento xalbal</t>
   </si>
   <si>
-    <t>13-31-0019-46</t>
-  </si>
-  <si>
-    <t>huehuetenango</t>
-  </si>
-  <si>
-    <t>santa ana huista</t>
-  </si>
-  <si>
     <t>cantón san juan</t>
   </si>
   <si>
-    <t>13-01-0421-46</t>
-  </si>
-  <si>
     <t>9no. callejón "b" 12-94 zona 4 sector los olivos "el terrero"</t>
   </si>
   <si>
-    <t>13-17-0075-46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">santa eulalia </t>
-  </si>
-  <si>
     <t xml:space="preserve">cantón centro </t>
   </si>
   <si>
-    <t>instituto nacional de educacion diversificada</t>
-  </si>
-  <si>
-    <t>16-14-0054-46</t>
-  </si>
-  <si>
-    <t>chahal</t>
-  </si>
-  <si>
     <t>barrio centro</t>
   </si>
   <si>
-    <t>16-01-0428-46</t>
-  </si>
-  <si>
     <t>diagonal 08 8-05 zona 8, barrio canton las casas</t>
   </si>
   <si>
+    <t>barrio san nicolas</t>
+  </si>
+  <si>
+    <t>casco urbano</t>
+  </si>
+  <si>
+    <t>barrio san juan</t>
+  </si>
+  <si>
+    <t>caserio pantocan</t>
+  </si>
+  <si>
+    <t>barrio el centro</t>
+  </si>
+  <si>
+    <t>aldea campur</t>
+  </si>
+  <si>
+    <t>5a calle final zona 1</t>
+  </si>
+  <si>
+    <t>barrio santa elena</t>
+  </si>
+  <si>
+    <t>tamahu</t>
+  </si>
+  <si>
+    <t>barrio san antonio</t>
+  </si>
+  <si>
+    <t>aldea san marcos sacsamani</t>
+  </si>
+  <si>
+    <t>caserio nuevo progreso panchisivic</t>
+  </si>
+  <si>
+    <t>2a. calle y 4a. avenida zona 3 frente al campo de aviacion</t>
+  </si>
+  <si>
+    <t>aldea concul</t>
+  </si>
+  <si>
+    <t>13 avenida 7-41, zona 2, barrio hacienda de la virgen</t>
+  </si>
+  <si>
+    <t>aldea chilasco</t>
+  </si>
+  <si>
+    <t>5 avenida 4-74 zona 1</t>
+  </si>
+  <si>
+    <t>barrio arriba</t>
+  </si>
+  <si>
+    <t>aldea san gabriel pantzuj</t>
+  </si>
+  <si>
+    <t>canton san juan</t>
+  </si>
+  <si>
+    <t>aldea san francisco</t>
+  </si>
+  <si>
+    <t>caserio chupel</t>
+  </si>
+  <si>
+    <t>aldea chicholon</t>
+  </si>
+  <si>
+    <t>aldea san rafael</t>
+  </si>
+  <si>
+    <t>6a ave. 4-10 zona 1</t>
+  </si>
+  <si>
+    <t>colonia nueva</t>
+  </si>
+  <si>
+    <t>barrio san lorenzo</t>
+  </si>
+  <si>
+    <t>barrio el centro san jacinto</t>
+  </si>
+  <si>
+    <t>5a. avenida 6-91 zona 1</t>
+  </si>
+  <si>
+    <t>9. callejon b 12-94 zona 4 sector los olivos el terrero</t>
+  </si>
+  <si>
+    <t>canton san sebastian</t>
+  </si>
+  <si>
+    <t>canton central</t>
+  </si>
+  <si>
+    <t>calle transito rojas, 4-82, zona 2, barrio san francisco</t>
+  </si>
+  <si>
+    <t>calzada juan jose bonilla, 3-02 zona 2 barrio san francisco</t>
+  </si>
+  <si>
+    <t>canton elena</t>
+  </si>
+  <si>
+    <t>barrio la reforma</t>
+  </si>
+  <si>
+    <t>kilometro 146.5</t>
+  </si>
+  <si>
+    <t>barrio camelias</t>
+  </si>
+  <si>
+    <t>barrio el llano</t>
+  </si>
+  <si>
+    <t>barrio san jose</t>
+  </si>
+  <si>
+    <t>barrio san pedro beleju, aldea beleju</t>
+  </si>
+  <si>
+    <t>canton vicotz</t>
+  </si>
+  <si>
+    <t>aldea saquixpec</t>
+  </si>
+  <si>
+    <t>20 calle final zona 4, colonia los celajes</t>
+  </si>
+  <si>
+    <t>20 calle final de la zona cuatro, colonia los celajes</t>
+  </si>
+  <si>
+    <t>5a. avenida arco gucumatz 1-61, zona 1</t>
+  </si>
+  <si>
+    <t>2 calle y 4 avenida zona 3, frente al campo de aviación</t>
+  </si>
+  <si>
+    <t>13 av. 7-41 zona 2</t>
+  </si>
+  <si>
+    <t>aldea chilascó</t>
+  </si>
+  <si>
+    <t>diagonal 8, 8-05 zona 8</t>
+  </si>
+  <si>
+    <t>14 calle 7-96 zona 2 barrio saraxoch</t>
+  </si>
+  <si>
+    <t>49823719</t>
+  </si>
+  <si>
+    <t>57036563</t>
+  </si>
+  <si>
+    <t>48942663</t>
+  </si>
+  <si>
+    <t>42062827/ 57831873</t>
+  </si>
+  <si>
+    <t>50062846</t>
+  </si>
+  <si>
+    <t>30216212</t>
+  </si>
+  <si>
     <t>inebined2012@gmail.com</t>
   </si>
   <si>
-    <t>16-11-0027-46</t>
-  </si>
-  <si>
-    <t>lanquin</t>
-  </si>
-  <si>
-    <t>barrio san nicolas</t>
-  </si>
-  <si>
-    <t>49823719</t>
-  </si>
-  <si>
     <t>anajuarezfigueroa2017@gmail.com</t>
   </si>
   <si>
-    <t>16-16-0049-46</t>
-  </si>
-  <si>
-    <t>la tinta</t>
-  </si>
-  <si>
-    <t>casco urbano</t>
-  </si>
-  <si>
     <t>inedlatinta@gmail.com</t>
   </si>
   <si>
-    <t>16-07-0117-46</t>
-  </si>
-  <si>
-    <t>panzos</t>
-  </si>
-  <si>
-    <t>barrio san juan</t>
-  </si>
-  <si>
-    <t>57036563</t>
-  </si>
-  <si>
     <t>umghectorcal@gmail.com</t>
   </si>
   <si>
-    <t>instituto nacional de educacion diversificada con orientacion en artes y oficios</t>
-  </si>
-  <si>
-    <t>16-03-0087-46</t>
-  </si>
-  <si>
-    <t>san cristobal verapaz</t>
-  </si>
-  <si>
-    <t>caserio pantocan</t>
-  </si>
-  <si>
     <t>artesyoficiosined2021@gmail.com</t>
   </si>
   <si>
-    <t>16-06-0090-46</t>
-  </si>
-  <si>
-    <t>san miguel tucuru</t>
-  </si>
-  <si>
-    <t>barrio el centro</t>
-  </si>
-  <si>
     <t>jjuanmeda@gmail.com</t>
   </si>
   <si>
-    <t>16-09-0386-46</t>
-  </si>
-  <si>
-    <t>san pedro carcha</t>
-  </si>
-  <si>
-    <t>aldea campur</t>
-  </si>
-  <si>
     <t>choccuz79@gmail.com</t>
   </si>
   <si>
-    <t>instituto tecnico diversificado de bachillerato en construccion</t>
-  </si>
-  <si>
-    <t>16-09-0720-46</t>
-  </si>
-  <si>
-    <t>5a calle final zona 1</t>
-  </si>
-  <si>
     <t>itdbc86@gmail.com</t>
   </si>
   <si>
-    <t>16-09-0830-46</t>
-  </si>
-  <si>
-    <t>16-02-0013-46</t>
-  </si>
-  <si>
-    <t>santa cruz verapaz</t>
-  </si>
-  <si>
-    <t>barrio santa elena</t>
-  </si>
-  <si>
     <t>erickroberto69@gmail.com</t>
   </si>
   <si>
-    <t>16-05-0017-46</t>
-  </si>
-  <si>
-    <t>tamahu</t>
-  </si>
-  <si>
-    <t>15-08-0200-46</t>
-  </si>
-  <si>
-    <t>purulha</t>
-  </si>
-  <si>
-    <t>barrio san antonio</t>
-  </si>
-  <si>
-    <t>15-08-0207-46</t>
-  </si>
-  <si>
-    <t>aldea san marcos sacsamani</t>
-  </si>
-  <si>
     <t>marcossacsamani@gmail.com</t>
   </si>
   <si>
-    <t>15-08-0219-46</t>
-  </si>
-  <si>
-    <t>caserio nuevo progreso panchisivic</t>
-  </si>
-  <si>
-    <t>48942663</t>
-  </si>
-  <si>
     <t>magnolia.capfortin@mineduc.edu.gt</t>
   </si>
   <si>
-    <t>15-03-0046-46</t>
-  </si>
-  <si>
-    <t>2a. calle y 4a. avenida zona 3 frente al campo de aviacion</t>
-  </si>
-  <si>
     <t>odygomez26@gmail.com</t>
   </si>
   <si>
-    <t>15-03-0085-46</t>
-  </si>
-  <si>
-    <t>aldea concul</t>
-  </si>
-  <si>
     <t>inedconcul@gmail.com</t>
   </si>
   <si>
-    <t>15-01-0087-46</t>
-  </si>
-  <si>
-    <t>salama</t>
-  </si>
-  <si>
-    <t>13 avenida 7-41, zona 2, barrio hacienda de la virgen</t>
-  </si>
-  <si>
     <t>rosynade@hotmail.com</t>
   </si>
   <si>
-    <t>15-01-0116-46</t>
-  </si>
-  <si>
-    <t>aldea chilasco</t>
-  </si>
-  <si>
     <t>inedchilasco@gmail.com</t>
   </si>
   <si>
-    <t>instituto nacional de administración de empresas</t>
-  </si>
-  <si>
-    <t>15-01-1274-46</t>
-  </si>
-  <si>
-    <t>5 avenida 4-74 zona 1</t>
-  </si>
-  <si>
     <t>walterx05@gmail.com</t>
   </si>
   <si>
-    <t>15-07-0036-46</t>
-  </si>
-  <si>
-    <t>san jeronimo</t>
-  </si>
-  <si>
-    <t>barrio arriba</t>
-  </si>
-  <si>
     <t>waleskasiana@gmail.com</t>
   </si>
   <si>
-    <t>15-02-0023-46</t>
-  </si>
-  <si>
-    <t>san miguel chicaj</t>
-  </si>
-  <si>
-    <t>aldea san gabriel pantzuj</t>
-  </si>
-  <si>
     <t>bachan010@gmail.com</t>
   </si>
   <si>
-    <t>15-02-0058-46</t>
-  </si>
-  <si>
-    <t>canton san juan</t>
-  </si>
-  <si>
     <t>rudyzoel@gmail.com</t>
   </si>
   <si>
-    <t>15-02-0094-46</t>
-  </si>
-  <si>
-    <t>aldea san francisco</t>
-  </si>
-  <si>
     <t>inedsanfraciscochicaj@gmail.com</t>
   </si>
   <si>
-    <t>15-02-0111-46</t>
-  </si>
-  <si>
-    <t>caserio chupel</t>
-  </si>
-  <si>
-    <t>42062827/ 57831873</t>
-  </si>
-  <si>
     <t>director saturnino celedonio ervinbachan19574@gmail.com</t>
   </si>
   <si>
-    <t>15-02-0125-46</t>
-  </si>
-  <si>
-    <t>aldea chicholon</t>
-  </si>
-  <si>
     <t>willieltriste@yahoo.com</t>
   </si>
   <si>
-    <t>15-02-0126-46</t>
-  </si>
-  <si>
-    <t>aldea san rafael</t>
-  </si>
-  <si>
     <t>rmali4g@yahoo.es</t>
   </si>
   <si>
-    <t>15-06-0006-46</t>
-  </si>
-  <si>
-    <t>santa cruz el chol</t>
-  </si>
-  <si>
     <t>erick.juarez@mineduc.gob.gt</t>
   </si>
   <si>
-    <t>instituto normal para varones de oriente</t>
-  </si>
-  <si>
-    <t>20-01-0036-46</t>
-  </si>
-  <si>
-    <t>6a ave. 4-10 zona 1</t>
-  </si>
-  <si>
     <t>balchape@gmail.com</t>
   </si>
   <si>
-    <t>20-08-0006-46</t>
-  </si>
-  <si>
-    <t>concepcion las minas</t>
-  </si>
-  <si>
-    <t>colonia nueva</t>
-  </si>
-  <si>
     <t>inedconce@gmail.com</t>
   </si>
   <si>
-    <t>instituto tecnologico oficial de la mancomunidad ch'orti'</t>
-  </si>
-  <si>
-    <t>20-04-0097-46</t>
-  </si>
-  <si>
-    <t>jocotan</t>
-  </si>
-  <si>
-    <t>barrio san lorenzo</t>
-  </si>
-  <si>
     <t>20-04-0097-46@mineduc.edu.gt</t>
   </si>
   <si>
-    <t>20-10-0013-46</t>
-  </si>
-  <si>
-    <t>san jacinto</t>
-  </si>
-  <si>
-    <t>barrio el centro san jacinto</t>
-  </si>
-  <si>
     <t>hazmendez49@gmail.com</t>
   </si>
   <si>
-    <t>13-27-0076-46</t>
-  </si>
-  <si>
-    <t>aguacatan</t>
-  </si>
-  <si>
-    <t>5a. avenida 6-91 zona 1</t>
-  </si>
-  <si>
     <t>ined.aguacatan19@gmail.com</t>
   </si>
   <si>
-    <t>13-01-0112-46</t>
-  </si>
-  <si>
     <t>huehueined10@gmail.com</t>
   </si>
   <si>
-    <t>13-01-0323-46</t>
-  </si>
-  <si>
-    <t>13-07-0067-46</t>
-  </si>
-  <si>
-    <t>jacaltenango</t>
-  </si>
-  <si>
-    <t>canton san sebastian</t>
-  </si>
-  <si>
-    <t>50062846</t>
-  </si>
-  <si>
     <t>jrcsshina@gmail.com</t>
   </si>
   <si>
-    <t>13-32-0035-46</t>
-  </si>
-  <si>
-    <t>union cantinil</t>
-  </si>
-  <si>
-    <t>canton central</t>
-  </si>
-  <si>
     <t>geisercarrillo6@gmail.com</t>
   </si>
   <si>
-    <t>instituto normal centroamericano para varones</t>
-  </si>
-  <si>
-    <t>21-01-0104-46</t>
-  </si>
-  <si>
-    <t>jalapa</t>
-  </si>
-  <si>
-    <t>calle transito rojas, 4-82, zona 2, barrio san francisco</t>
-  </si>
-  <si>
     <t>incavja1920@hotmail.com</t>
   </si>
   <si>
-    <t>21-01-0391-46</t>
-  </si>
-  <si>
-    <t>calzada juan jose bonilla, 3-02 zona 2 barrio san francisco</t>
-  </si>
-  <si>
-    <t>30216212</t>
-  </si>
-  <si>
     <t>inedjalapa9222@gmail.com</t>
   </si>
   <si>
-    <t>21-07-0063-46</t>
-  </si>
-  <si>
-    <t>mataquescuintla</t>
-  </si>
-  <si>
-    <t>canton elena</t>
-  </si>
-  <si>
     <t>institutonacionalcantonelena@gmail.com</t>
   </si>
   <si>
-    <t>21-06-0021-46</t>
-  </si>
-  <si>
-    <t>monjas</t>
-  </si>
-  <si>
-    <t>barrio la reforma</t>
-  </si>
-  <si>
     <t>ined.monjas06@gmail.com</t>
   </si>
   <si>
-    <t>escuela normal regional de oriente "licenciado clemente marroquin rojas"</t>
-  </si>
-  <si>
-    <t>21-06-0239-46</t>
-  </si>
-  <si>
-    <t>kilometro 146.5</t>
-  </si>
-  <si>
     <t>enromonjasjalapa@hotmail.com</t>
   </si>
   <si>
-    <t>21-05-0017-46</t>
-  </si>
-  <si>
-    <t>san carlos alzatate</t>
-  </si>
-  <si>
-    <t>barrio camelias</t>
-  </si>
-  <si>
     <t>inedsancarlosalzatate@hotmail.com</t>
   </si>
   <si>
-    <t>21-03-0010-46</t>
-  </si>
-  <si>
-    <t>san luis jilotepeque</t>
-  </si>
-  <si>
-    <t>barrio el llano</t>
-  </si>
-  <si>
     <t>ciriacodamian@hotmail.com</t>
   </si>
   <si>
-    <t>21-03-0034-46</t>
-  </si>
-  <si>
     <t>ciriacodamianm@gmail.com</t>
   </si>
   <si>
-    <t>21-02-0050-46</t>
-  </si>
-  <si>
-    <t>san pedro pinula</t>
-  </si>
-  <si>
-    <t>barrio san jose</t>
-  </si>
-  <si>
     <t>botonielperez@hotmail.com</t>
   </si>
   <si>
-    <t>instituto nacional de educacion diversificada -ined-</t>
-  </si>
-  <si>
-    <t>14-19-0055-46</t>
-  </si>
-  <si>
-    <t>chicaman</t>
-  </si>
-  <si>
-    <t>barrio san pedro beleju, aldea beleju</t>
-  </si>
-  <si>
     <t>alfacolocho@gmail.com</t>
   </si>
   <si>
-    <t>14-10-0059-46</t>
-  </si>
-  <si>
-    <t>cunen</t>
-  </si>
-  <si>
     <t>kennethagus@hotmail.es</t>
   </si>
   <si>
-    <t>14-13-0068-46</t>
-  </si>
-  <si>
-    <t>nebaj</t>
-  </si>
-  <si>
-    <t>canton vicotz</t>
-  </si>
-  <si>
     <t>apoloniomendoza7@yahoo.es</t>
   </si>
   <si>
-    <t>14-15-0103-46</t>
-  </si>
-  <si>
-    <t>san miguel uspantan</t>
-  </si>
-  <si>
-    <t>aldea saquixpec</t>
-  </si>
-  <si>
     <t>tipacti35@gmail.com</t>
   </si>
   <si>
-    <t>14-01-0112-46</t>
-  </si>
-  <si>
-    <t>20 calle final zona 4, colonia los celajes</t>
-  </si>
-  <si>
     <t>jpereirag@mineduc.gob.gt</t>
   </si>
   <si>
-    <t>instituto tecnico de nivel medio</t>
-  </si>
-  <si>
-    <t>14-01-0236-46</t>
-  </si>
-  <si>
-    <t>20 calle final de la zona cuatro, colonia los celajes</t>
-  </si>
-  <si>
     <t>morhody@gmail.com</t>
   </si>
   <si>
-    <t>14-06-0020-46</t>
-  </si>
-  <si>
-    <t>5a. avenida arco gucumatz 1-61, zona 1</t>
-  </si>
-  <si>
     <t>inedchichi@gmail.com</t>
   </si>
   <si>
-    <t>15-06-0009-46</t>
-  </si>
-  <si>
     <t>obdulioerick@yahoo.es</t>
   </si>
   <si>
+    <t>rmalia4g@yahoo.com</t>
+  </si>
+  <si>
+    <t>rosynadez@gmail.com</t>
+  </si>
+  <si>
+    <t>lemaqg@gmail.com</t>
+  </si>
+  <si>
+    <t>bachano10@gmail.com</t>
+  </si>
+  <si>
+    <t>waosisortiz1988@gmail.com</t>
+  </si>
+  <si>
+    <t>liliangramajo26@gmail.com</t>
+  </si>
+  <si>
+    <t>joeldavidlemsuram@gmail.com</t>
+  </si>
+  <si>
+    <t>hehelson@yahoo.com</t>
+  </si>
+  <si>
     <t>erick obdulio juarez</t>
   </si>
   <si>
     <t>fredy otoniek raymundo rodriguez</t>
   </si>
   <si>
-    <t>rmalia4g@yahoo.com</t>
-  </si>
-  <si>
     <t>reyna amalia rojas galiego</t>
   </si>
   <si>
-    <t>san jeranimo</t>
-  </si>
-  <si>
     <t>waleska judithpicon siana de canahui</t>
   </si>
   <si>
     <t>rudy zoel rodriguez</t>
   </si>
   <si>
-    <t>2 calle y 4 avenida zona 3, frente al campo de aviación</t>
-  </si>
-  <si>
     <t>odilia mirtala gomez juarez</t>
   </si>
   <si>
     <t>walter orlando juarez</t>
   </si>
   <si>
-    <t>13 av. 7-41 zona 2</t>
-  </si>
-  <si>
-    <t>rosynadez@gmail.com</t>
-  </si>
-  <si>
     <t>rosalina nadayda toj</t>
   </si>
   <si>
-    <t>aldea chilascó</t>
-  </si>
-  <si>
-    <t>lemaqg@gmail.com</t>
-  </si>
-  <si>
     <t>lester mateo quej garcia</t>
   </si>
   <si>
-    <t>bachano10@gmail.com</t>
-  </si>
-  <si>
     <t>mynor estuardo bachan perez</t>
   </si>
   <si>
-    <t>waosisortiz1988@gmail.com</t>
-  </si>
-  <si>
     <t>walter oseas ortiz sis</t>
   </si>
   <si>
-    <t>liliangramajo26@gmail.com</t>
-  </si>
-  <si>
     <t>lilian maria gramajo garrido de tello</t>
   </si>
   <si>
-    <t>joeldavidlemsuram@gmail.com</t>
-  </si>
-  <si>
     <t>joel david lem suram</t>
   </si>
   <si>
     <t>erik roberto cu pop</t>
   </si>
   <si>
-    <t>diagonal 8, 8-05 zona 8</t>
-  </si>
-  <si>
-    <t>hehelson@yahoo.com</t>
-  </si>
-  <si>
     <t>helson marco antonio chen</t>
   </si>
   <si>
-    <t>instituto tócnico de diversificado bachillerato en contruccion</t>
-  </si>
-  <si>
-    <t>14 calle 7-96 zona 2 barrio saraxoch</t>
-  </si>
-  <si>
     <t>angel gustavo rivera argeta</t>
   </si>
   <si>
-    <t>instituto tócnico diversificado de bachillerato en contruccion</t>
-  </si>
-  <si>
     <t>ana mariela juarez figuero</t>
   </si>
   <si>
     <t>josefina choc cuz</t>
   </si>
   <si>
-    <t xml:space="preserve">guatemala </t>
-  </si>
-  <si>
-    <t>9. callejon b 12-94 zona 4 sector los olivos el terrero</t>
-  </si>
-  <si>
-    <t>chichicastenango</t>
-  </si>
-  <si>
-    <t>santa catarina ixtahuacán</t>
-  </si>
-  <si>
-    <t>el chal</t>
-  </si>
-  <si>
-    <t>santa cruz muluá</t>
-  </si>
-  <si>
-    <t>santiago atitlán</t>
-  </si>
-  <si>
-    <t>san martin zapotitlán</t>
+    <t>jocotán</t>
+  </si>
+  <si>
+    <t>uspantán</t>
+  </si>
+  <si>
+    <t>san miguel tucurú</t>
+  </si>
+  <si>
+    <t>san bartolo</t>
+  </si>
+  <si>
+    <t>santa catalina la tinta</t>
+  </si>
+  <si>
+    <t>san pablo jocopilas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1682,11 +1673,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1729,12 +1715,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1753,7 +1738,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1795,7 +1780,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1827,9 +1812,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1861,6 +1864,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2040,13 +2061,8 @@
   <dimension ref="A1:K162"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="39.77734375" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" customWidth="1"/>
-    <col min="6" max="6" width="61.21875" customWidth="1"/>
-    <col min="10" max="10" width="37.21875" customWidth="1"/>
-    <col min="11" max="11" width="37.109375" customWidth="1"/>
+    <col min="4" max="4" width="37.5546875" customWidth="1"/>
+    <col min="5" max="5" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -2092,16 +2108,16 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>209</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="J2">
         <v>25</v>
@@ -2115,19 +2131,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>539</v>
+        <v>210</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>232</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>319</v>
       </c>
       <c r="J3">
         <v>25</v>
@@ -2141,19 +2157,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>209</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>320</v>
       </c>
       <c r="J4">
         <v>25</v>
@@ -2167,19 +2183,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>539</v>
+        <v>210</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>234</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>321</v>
       </c>
       <c r="J5">
         <v>25</v>
@@ -2193,19 +2209,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>539</v>
+        <v>210</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>232</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>322</v>
       </c>
       <c r="J6">
         <v>25</v>
@@ -2219,19 +2235,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>209</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>235</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>323</v>
       </c>
       <c r="J7">
         <v>25</v>
@@ -2245,19 +2261,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>539</v>
+        <v>210</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>232</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>324</v>
       </c>
       <c r="J8">
         <v>25</v>
@@ -2271,19 +2287,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>539</v>
+        <v>210</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>325</v>
       </c>
       <c r="J9">
         <v>25</v>
@@ -2297,19 +2313,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>51</v>
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>211</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>236</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>326</v>
       </c>
       <c r="J10">
         <v>25</v>
@@ -2323,19 +2339,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>211</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>237</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>327</v>
       </c>
       <c r="J11">
         <v>25</v>
@@ -2349,19 +2365,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>328</v>
       </c>
       <c r="J12">
         <v>25</v>
@@ -2375,19 +2391,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>211</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>239</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>329</v>
       </c>
       <c r="J13">
         <v>11</v>
@@ -2401,19 +2417,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>211</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>239</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>330</v>
       </c>
       <c r="J14">
         <v>25</v>
@@ -2427,19 +2443,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>331</v>
       </c>
       <c r="J15">
         <v>25</v>
@@ -2453,19 +2469,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>332</v>
       </c>
       <c r="J16">
         <v>25</v>
@@ -2479,19 +2495,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>333</v>
       </c>
       <c r="J17">
         <v>25</v>
@@ -2505,19 +2521,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="E18" t="s">
-        <v>542</v>
+        <v>241</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>334</v>
       </c>
       <c r="J18">
         <v>25</v>
@@ -2531,19 +2547,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="E19" t="s">
-        <v>545</v>
+        <v>242</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>335</v>
       </c>
       <c r="J19">
         <v>25</v>
@@ -2557,19 +2573,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>243</v>
       </c>
       <c r="F20" t="s">
-        <v>72</v>
+        <v>336</v>
       </c>
       <c r="J20">
         <v>25</v>
@@ -2583,19 +2599,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="E21" t="s">
-        <v>544</v>
+        <v>244</v>
       </c>
       <c r="F21" t="s">
-        <v>75</v>
+        <v>337</v>
       </c>
       <c r="J21">
         <v>25</v>
@@ -2609,19 +2625,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="E22" t="s">
-        <v>546</v>
+        <v>245</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="J22">
         <v>25</v>
@@ -2635,19 +2651,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="E23" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="J23">
         <v>25</v>
@@ -2661,19 +2677,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>246</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>340</v>
       </c>
       <c r="J24">
         <v>25</v>
@@ -2687,19 +2703,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="E25" t="s">
-        <v>86</v>
+        <v>247</v>
       </c>
       <c r="F25" t="s">
-        <v>87</v>
+        <v>341</v>
       </c>
       <c r="J25">
         <v>25</v>
@@ -2713,19 +2729,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="F26" t="s">
-        <v>90</v>
+        <v>342</v>
       </c>
       <c r="J26">
         <v>25</v>
@@ -2739,19 +2755,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
         <v>91</v>
       </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
       <c r="D27" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="E27" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
       <c r="F27" t="s">
-        <v>95</v>
+        <v>343</v>
       </c>
       <c r="J27">
         <v>25</v>
@@ -2765,19 +2781,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="E28" t="s">
-        <v>98</v>
+        <v>249</v>
       </c>
       <c r="F28" t="s">
-        <v>99</v>
+        <v>344</v>
       </c>
       <c r="J28">
         <v>25</v>
@@ -2791,19 +2807,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="E29" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="F29" t="s">
-        <v>101</v>
+        <v>345</v>
       </c>
       <c r="J29">
         <v>25</v>
@@ -2817,19 +2833,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="E30" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="F30" t="s">
-        <v>104</v>
+        <v>346</v>
       </c>
       <c r="J30">
         <v>25</v>
@@ -2843,19 +2859,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="E31" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="F31" t="s">
-        <v>108</v>
+        <v>347</v>
       </c>
       <c r="J31">
         <v>25</v>
@@ -2869,19 +2885,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="E32" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="F32" t="s">
-        <v>111</v>
+        <v>348</v>
       </c>
       <c r="J32">
         <v>25</v>
@@ -2895,19 +2911,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="E33" t="s">
-        <v>114</v>
+        <v>250</v>
       </c>
       <c r="F33" t="s">
-        <v>115</v>
+        <v>349</v>
       </c>
       <c r="J33">
         <v>25</v>
@@ -2921,19 +2937,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="E34" t="s">
-        <v>118</v>
+        <v>251</v>
       </c>
       <c r="F34" t="s">
-        <v>119</v>
+        <v>350</v>
       </c>
       <c r="J34">
         <v>25</v>
@@ -2947,19 +2963,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="E35" t="s">
-        <v>123</v>
+        <v>252</v>
       </c>
       <c r="F35" t="s">
-        <v>124</v>
+        <v>351</v>
       </c>
       <c r="J35">
         <v>25</v>
@@ -2973,19 +2989,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="E36" t="s">
-        <v>126</v>
+        <v>253</v>
       </c>
       <c r="F36" t="s">
-        <v>127</v>
+        <v>352</v>
       </c>
       <c r="J36">
         <v>25</v>
@@ -2999,19 +3015,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="E37" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="F37" t="s">
-        <v>130</v>
+        <v>353</v>
       </c>
       <c r="J37">
         <v>25</v>
@@ -3025,19 +3041,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="E38" t="s">
-        <v>132</v>
+        <v>254</v>
       </c>
       <c r="F38" t="s">
-        <v>133</v>
+        <v>354</v>
       </c>
       <c r="J38">
         <v>25</v>
@@ -3051,19 +3067,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="E39" t="s">
-        <v>543</v>
+        <v>255</v>
       </c>
       <c r="F39" t="s">
-        <v>137</v>
+        <v>355</v>
       </c>
       <c r="J39">
         <v>25</v>
@@ -3077,19 +3093,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="E40" t="s">
-        <v>139</v>
+        <v>256</v>
       </c>
       <c r="F40" t="s">
-        <v>140</v>
+        <v>356</v>
       </c>
       <c r="J40">
         <v>25</v>
@@ -3103,19 +3119,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="E41" t="s">
-        <v>142</v>
+        <v>257</v>
       </c>
       <c r="F41" t="s">
-        <v>143</v>
+        <v>357</v>
       </c>
       <c r="J41">
         <v>25</v>
@@ -3129,19 +3145,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="E42" t="s">
-        <v>142</v>
+        <v>257</v>
       </c>
       <c r="F42" t="s">
-        <v>145</v>
+        <v>358</v>
       </c>
       <c r="J42">
         <v>25</v>
@@ -3155,19 +3171,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>146</v>
+        <v>33</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="E43" t="s">
-        <v>149</v>
+        <v>258</v>
       </c>
       <c r="F43" t="s">
-        <v>150</v>
+        <v>359</v>
       </c>
       <c r="J43">
         <v>25</v>
@@ -3181,19 +3197,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="D44" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="E44" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="F44" t="s">
-        <v>154</v>
+        <v>360</v>
       </c>
       <c r="J44">
         <v>25</v>
@@ -3207,19 +3223,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="C45" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="D45" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="E45" t="s">
-        <v>157</v>
+        <v>260</v>
       </c>
       <c r="F45" t="s">
-        <v>158</v>
+        <v>361</v>
       </c>
       <c r="J45">
         <v>25</v>
@@ -3233,19 +3249,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>159</v>
+        <v>36</v>
       </c>
       <c r="C46" t="s">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="D46" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="E46" t="s">
-        <v>161</v>
+        <v>261</v>
       </c>
       <c r="F46" t="s">
-        <v>162</v>
+        <v>362</v>
       </c>
       <c r="J46">
         <v>25</v>
@@ -3259,19 +3275,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>163</v>
+        <v>37</v>
       </c>
       <c r="C47" t="s">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="D47" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="E47" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="F47" t="s">
-        <v>165</v>
+        <v>363</v>
       </c>
       <c r="J47">
         <v>25</v>
@@ -3285,19 +3301,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>166</v>
+        <v>38</v>
       </c>
       <c r="C48" t="s">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="D48" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="E48" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="F48" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
       <c r="J48">
         <v>25</v>
@@ -3311,19 +3327,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="D49" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="E49" t="s">
-        <v>171</v>
+        <v>262</v>
       </c>
       <c r="F49" t="s">
-        <v>172</v>
+        <v>365</v>
       </c>
       <c r="J49">
         <v>25</v>
@@ -3337,19 +3353,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>173</v>
+        <v>39</v>
       </c>
       <c r="C50" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="E50" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="F50" t="s">
-        <v>175</v>
+        <v>366</v>
       </c>
       <c r="J50">
         <v>25</v>
@@ -3363,19 +3379,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>176</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>177</v>
+        <v>115</v>
       </c>
       <c r="D51" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="E51" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="F51" t="s">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="J51">
         <v>25</v>
@@ -3389,19 +3405,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>179</v>
+        <v>41</v>
       </c>
       <c r="C52" t="s">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="E52" t="s">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="F52" t="s">
-        <v>182</v>
+        <v>368</v>
       </c>
       <c r="J52">
         <v>25</v>
@@ -3415,19 +3431,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>183</v>
+        <v>42</v>
       </c>
       <c r="C53" t="s">
-        <v>184</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E53" t="s">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="F53" t="s">
-        <v>187</v>
+        <v>369</v>
       </c>
       <c r="J53">
         <v>25</v>
@@ -3441,19 +3457,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>188</v>
+        <v>118</v>
       </c>
       <c r="D54" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E54" t="s">
-        <v>190</v>
+        <v>265</v>
       </c>
       <c r="F54" t="s">
-        <v>191</v>
+        <v>370</v>
       </c>
       <c r="J54">
         <v>25</v>
@@ -3467,19 +3483,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
       <c r="D55" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E55" t="s">
-        <v>193</v>
+        <v>266</v>
       </c>
       <c r="F55" t="s">
-        <v>194</v>
+        <v>371</v>
       </c>
       <c r="J55">
         <v>25</v>
@@ -3493,19 +3509,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="D56" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E56" t="s">
-        <v>196</v>
+        <v>267</v>
       </c>
       <c r="F56" t="s">
-        <v>197</v>
+        <v>372</v>
       </c>
       <c r="J56">
         <v>25</v>
@@ -3519,19 +3535,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>198</v>
+        <v>43</v>
       </c>
       <c r="C57" t="s">
-        <v>199</v>
+        <v>121</v>
       </c>
       <c r="D57" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E57" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="F57" t="s">
-        <v>201</v>
+        <v>373</v>
       </c>
       <c r="J57">
         <v>25</v>
@@ -3545,19 +3561,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>202</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E58" t="s">
-        <v>203</v>
+        <v>268</v>
       </c>
       <c r="F58" t="s">
-        <v>204</v>
+        <v>374</v>
       </c>
       <c r="J58">
         <v>25</v>
@@ -3571,19 +3587,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E59" t="s">
-        <v>206</v>
+        <v>541</v>
       </c>
       <c r="F59" t="s">
-        <v>207</v>
+        <v>375</v>
       </c>
       <c r="J59">
         <v>25</v>
@@ -3597,19 +3613,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="C60" t="s">
-        <v>208</v>
+        <v>124</v>
       </c>
       <c r="D60" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E60" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="F60" t="s">
-        <v>209</v>
+        <v>376</v>
       </c>
       <c r="J60">
         <v>25</v>
@@ -3623,19 +3639,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D61" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E61" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F61" t="s">
-        <v>212</v>
+        <v>377</v>
       </c>
       <c r="J61">
         <v>25</v>
@@ -3649,19 +3665,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>213</v>
+        <v>44</v>
       </c>
       <c r="C62" t="s">
-        <v>214</v>
+        <v>126</v>
       </c>
       <c r="D62" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E62" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F62" t="s">
-        <v>215</v>
+        <v>378</v>
       </c>
       <c r="J62">
         <v>25</v>
@@ -3675,19 +3691,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>216</v>
+        <v>45</v>
       </c>
       <c r="C63" t="s">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="D63" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E63" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="F63" t="s">
-        <v>219</v>
+        <v>379</v>
       </c>
       <c r="J63">
         <v>25</v>
@@ -3701,19 +3717,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>220</v>
+        <v>128</v>
       </c>
       <c r="D64" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E64" t="s">
-        <v>221</v>
+        <v>270</v>
       </c>
       <c r="F64" t="s">
-        <v>222</v>
+        <v>380</v>
       </c>
       <c r="J64">
         <v>25</v>
@@ -3727,19 +3743,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>223</v>
+        <v>129</v>
       </c>
       <c r="D65" t="s">
         <v>224</v>
       </c>
       <c r="E65" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="F65" t="s">
-        <v>226</v>
+        <v>381</v>
       </c>
       <c r="J65">
         <v>25</v>
@@ -3753,19 +3769,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>227</v>
+        <v>46</v>
       </c>
       <c r="C66" t="s">
-        <v>228</v>
+        <v>130</v>
       </c>
       <c r="D66" t="s">
         <v>224</v>
       </c>
       <c r="E66" t="s">
-        <v>229</v>
+        <v>272</v>
       </c>
       <c r="F66" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="J66">
         <v>14</v>
@@ -3779,19 +3795,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>231</v>
+        <v>131</v>
       </c>
       <c r="D67" t="s">
         <v>224</v>
       </c>
       <c r="E67" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="F67" t="s">
-        <v>233</v>
+        <v>383</v>
       </c>
       <c r="J67">
         <v>25</v>
@@ -3805,19 +3821,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>234</v>
+        <v>132</v>
       </c>
       <c r="D68" t="s">
         <v>224</v>
       </c>
       <c r="E68" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="F68" t="s">
-        <v>236</v>
+        <v>384</v>
       </c>
       <c r="J68">
         <v>25</v>
@@ -3831,19 +3847,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>237</v>
+        <v>47</v>
       </c>
       <c r="C69" t="s">
-        <v>238</v>
+        <v>133</v>
       </c>
       <c r="D69" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="E69" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="F69" t="s">
-        <v>241</v>
+        <v>385</v>
       </c>
       <c r="J69">
         <v>25</v>
@@ -3857,19 +3873,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="D70" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="E70" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="F70" t="s">
-        <v>244</v>
+        <v>386</v>
       </c>
       <c r="J70">
         <v>25</v>
@@ -3883,19 +3899,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="D71" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="E71" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="F71" t="s">
-        <v>241</v>
+        <v>385</v>
       </c>
       <c r="J71">
         <v>25</v>
@@ -3909,19 +3925,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>246</v>
+        <v>48</v>
       </c>
       <c r="C72" t="s">
-        <v>247</v>
+        <v>136</v>
       </c>
       <c r="D72" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="E72" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="F72" t="s">
-        <v>249</v>
+        <v>387</v>
       </c>
       <c r="J72">
         <v>25</v>
@@ -3935,19 +3951,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C73" t="s">
-        <v>251</v>
+        <v>137</v>
       </c>
       <c r="D73" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="E73" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="F73" t="s">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="J73">
         <v>25</v>
@@ -3961,19 +3977,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>254</v>
+        <v>50</v>
       </c>
       <c r="C74" t="s">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="D74" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="E74" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="F74" t="s">
-        <v>256</v>
+        <v>388</v>
       </c>
       <c r="J74">
         <v>25</v>
@@ -3987,19 +4003,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>257</v>
+        <v>139</v>
       </c>
       <c r="D75" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="E75" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="F75" t="s">
-        <v>259</v>
+        <v>389</v>
       </c>
       <c r="J75">
         <v>25</v>
@@ -4013,19 +4029,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C76" t="s">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="D76" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="E76" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="F76" t="s">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="J76">
         <v>25</v>
@@ -4039,19 +4055,19 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>262</v>
+        <v>141</v>
       </c>
       <c r="D77" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="E77" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="F77" t="s">
-        <v>265</v>
+        <v>390</v>
       </c>
       <c r="J77">
         <v>25</v>
@@ -4065,19 +4081,19 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C78" t="s">
-        <v>266</v>
+        <v>142</v>
       </c>
       <c r="D78" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="E78" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="F78" t="s">
-        <v>268</v>
+        <v>391</v>
       </c>
       <c r="J78">
         <v>25</v>
@@ -4091,19 +4107,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C79" t="s">
-        <v>269</v>
+        <v>143</v>
       </c>
       <c r="D79" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="E79" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="F79" t="s">
-        <v>271</v>
+        <v>392</v>
       </c>
       <c r="J79">
         <v>25</v>
@@ -4117,19 +4133,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C80" t="s">
-        <v>272</v>
+        <v>144</v>
       </c>
       <c r="D80" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="E80" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="F80" t="s">
-        <v>275</v>
+        <v>393</v>
       </c>
       <c r="J80">
         <v>25</v>
@@ -4143,19 +4159,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C81" t="s">
-        <v>276</v>
+        <v>145</v>
       </c>
       <c r="D81" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="E81" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="F81" t="s">
-        <v>278</v>
+        <v>394</v>
       </c>
       <c r="J81">
         <v>25</v>
@@ -4169,19 +4185,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C82" t="s">
-        <v>279</v>
+        <v>146</v>
       </c>
       <c r="D82" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="E82" t="s">
-        <v>280</v>
+        <v>543</v>
       </c>
       <c r="F82" t="s">
-        <v>281</v>
+        <v>395</v>
       </c>
       <c r="J82">
         <v>25</v>
@@ -4195,19 +4211,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C83" t="s">
-        <v>282</v>
+        <v>147</v>
       </c>
       <c r="D83" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="E83" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F83" t="s">
-        <v>284</v>
+        <v>396</v>
       </c>
       <c r="J83">
         <v>25</v>
@@ -4221,19 +4237,19 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C84" t="s">
-        <v>285</v>
+        <v>148</v>
       </c>
       <c r="D84" t="s">
+        <v>229</v>
+      </c>
+      <c r="E84" t="s">
         <v>286</v>
       </c>
-      <c r="E84" t="s">
-        <v>287</v>
-      </c>
       <c r="F84" t="s">
-        <v>288</v>
+        <v>397</v>
       </c>
       <c r="J84">
         <v>25</v>
@@ -4247,19 +4263,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>289</v>
+        <v>51</v>
       </c>
       <c r="C85" t="s">
-        <v>290</v>
+        <v>149</v>
       </c>
       <c r="D85" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="E85" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F85" t="s">
-        <v>292</v>
+        <v>398</v>
       </c>
       <c r="J85">
         <v>25</v>
@@ -4273,19 +4289,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>293</v>
+        <v>52</v>
       </c>
       <c r="C86" t="s">
-        <v>294</v>
+        <v>150</v>
       </c>
       <c r="D86" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="E86" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="F86" t="s">
-        <v>296</v>
+        <v>399</v>
       </c>
       <c r="J86">
         <v>25</v>
@@ -4299,19 +4315,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>297</v>
+        <v>53</v>
       </c>
       <c r="C87" t="s">
-        <v>298</v>
+        <v>151</v>
       </c>
       <c r="D87" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="E87" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="F87" t="s">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J87">
         <v>25</v>
@@ -4325,19 +4341,19 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>301</v>
+        <v>152</v>
       </c>
       <c r="D88" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="E88" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="F88" t="s">
-        <v>304</v>
+        <v>401</v>
       </c>
       <c r="J88">
         <v>25</v>
@@ -4351,19 +4367,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>305</v>
+        <v>153</v>
       </c>
       <c r="D89" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="E89" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="F89" t="s">
-        <v>306</v>
+        <v>402</v>
       </c>
       <c r="J89">
         <v>25</v>
@@ -4377,19 +4393,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C90" t="s">
-        <v>307</v>
+        <v>154</v>
       </c>
       <c r="D90" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="E90" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="F90" t="s">
-        <v>309</v>
+        <v>403</v>
       </c>
       <c r="J90">
         <v>25</v>
@@ -4403,19 +4419,19 @@
         <v>219</v>
       </c>
       <c r="B91" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C91" t="s">
-        <v>311</v>
+        <v>155</v>
       </c>
       <c r="D91" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E91" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="F91" t="s">
-        <v>313</v>
+        <v>404</v>
       </c>
       <c r="J91">
         <v>50</v>
@@ -4429,25 +4445,25 @@
         <v>220</v>
       </c>
       <c r="B92" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C92" t="s">
-        <v>314</v>
+        <v>156</v>
       </c>
       <c r="D92" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E92" t="s">
-        <v>193</v>
+        <v>266</v>
       </c>
       <c r="F92" t="s">
-        <v>315</v>
+        <v>405</v>
       </c>
       <c r="G92">
         <v>77930045</v>
       </c>
       <c r="H92" t="s">
-        <v>316</v>
+        <v>463</v>
       </c>
       <c r="J92">
         <v>25</v>
@@ -4461,25 +4477,25 @@
         <v>221</v>
       </c>
       <c r="B93" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C93" t="s">
-        <v>317</v>
+        <v>157</v>
       </c>
       <c r="D93" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E93" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="F93" t="s">
-        <v>319</v>
+        <v>406</v>
       </c>
       <c r="G93" t="s">
-        <v>320</v>
+        <v>457</v>
       </c>
       <c r="H93" t="s">
-        <v>321</v>
+        <v>464</v>
       </c>
       <c r="J93">
         <v>25</v>
@@ -4493,25 +4509,25 @@
         <v>222</v>
       </c>
       <c r="B94" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C94" t="s">
-        <v>322</v>
+        <v>158</v>
       </c>
       <c r="D94" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E94" t="s">
-        <v>323</v>
+        <v>542</v>
       </c>
       <c r="F94" t="s">
-        <v>324</v>
+        <v>407</v>
       </c>
       <c r="G94">
         <v>51625336</v>
       </c>
       <c r="H94" t="s">
-        <v>325</v>
+        <v>465</v>
       </c>
       <c r="J94">
         <v>75</v>
@@ -4525,25 +4541,25 @@
         <v>223</v>
       </c>
       <c r="B95" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C95" t="s">
-        <v>326</v>
+        <v>159</v>
       </c>
       <c r="D95" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E95" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
       <c r="F95" t="s">
-        <v>328</v>
+        <v>408</v>
       </c>
       <c r="G95" t="s">
-        <v>329</v>
+        <v>458</v>
       </c>
       <c r="H95" t="s">
-        <v>330</v>
+        <v>466</v>
       </c>
       <c r="J95">
         <v>25</v>
@@ -4557,25 +4573,25 @@
         <v>224</v>
       </c>
       <c r="B96" t="s">
-        <v>331</v>
+        <v>55</v>
       </c>
       <c r="C96" t="s">
-        <v>332</v>
+        <v>160</v>
       </c>
       <c r="D96" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E96" t="s">
-        <v>333</v>
+        <v>295</v>
       </c>
       <c r="F96" t="s">
-        <v>334</v>
+        <v>409</v>
       </c>
       <c r="G96">
         <v>55288589</v>
       </c>
       <c r="H96" t="s">
-        <v>335</v>
+        <v>467</v>
       </c>
       <c r="J96">
         <v>25</v>
@@ -4589,25 +4605,25 @@
         <v>225</v>
       </c>
       <c r="B97" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C97" t="s">
-        <v>336</v>
+        <v>161</v>
       </c>
       <c r="D97" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E97" t="s">
-        <v>337</v>
+        <v>540</v>
       </c>
       <c r="F97" t="s">
-        <v>338</v>
+        <v>410</v>
       </c>
       <c r="G97">
         <v>40232213</v>
       </c>
       <c r="H97" t="s">
-        <v>339</v>
+        <v>468</v>
       </c>
       <c r="J97">
         <v>25</v>
@@ -4621,25 +4637,25 @@
         <v>226</v>
       </c>
       <c r="B98" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C98" t="s">
-        <v>340</v>
+        <v>162</v>
       </c>
       <c r="D98" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E98" t="s">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="F98" t="s">
-        <v>342</v>
+        <v>411</v>
       </c>
       <c r="G98">
         <v>55245770</v>
       </c>
       <c r="H98" t="s">
-        <v>343</v>
+        <v>469</v>
       </c>
       <c r="J98">
         <v>25</v>
@@ -4653,25 +4669,25 @@
         <v>227</v>
       </c>
       <c r="B99" t="s">
-        <v>344</v>
+        <v>56</v>
       </c>
       <c r="C99" t="s">
-        <v>345</v>
+        <v>163</v>
       </c>
       <c r="D99" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E99" t="s">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="F99" t="s">
-        <v>346</v>
+        <v>412</v>
       </c>
       <c r="G99">
         <v>79515766</v>
       </c>
       <c r="H99" t="s">
-        <v>347</v>
+        <v>470</v>
       </c>
       <c r="J99">
         <v>25</v>
@@ -4685,25 +4701,25 @@
         <v>228</v>
       </c>
       <c r="B100" t="s">
-        <v>344</v>
+        <v>56</v>
       </c>
       <c r="C100" t="s">
-        <v>348</v>
+        <v>164</v>
       </c>
       <c r="D100" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E100" t="s">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="F100" t="s">
-        <v>346</v>
+        <v>412</v>
       </c>
       <c r="G100">
         <v>44457071</v>
       </c>
       <c r="H100" t="s">
-        <v>347</v>
+        <v>470</v>
       </c>
       <c r="J100">
         <v>25</v>
@@ -4717,25 +4733,25 @@
         <v>229</v>
       </c>
       <c r="B101" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C101" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
       <c r="D101" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E101" t="s">
-        <v>350</v>
+        <v>297</v>
       </c>
       <c r="F101" t="s">
-        <v>351</v>
+        <v>413</v>
       </c>
       <c r="G101">
         <v>57767683</v>
       </c>
       <c r="H101" t="s">
-        <v>352</v>
+        <v>471</v>
       </c>
       <c r="J101">
         <v>25</v>
@@ -4749,19 +4765,19 @@
         <v>230</v>
       </c>
       <c r="B102" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C102" t="s">
-        <v>353</v>
+        <v>166</v>
       </c>
       <c r="D102" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E102" t="s">
-        <v>354</v>
+        <v>298</v>
       </c>
       <c r="F102" t="s">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="G102">
         <v>58034583</v>
@@ -4778,19 +4794,19 @@
         <v>231</v>
       </c>
       <c r="B103" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C103" t="s">
-        <v>355</v>
+        <v>167</v>
       </c>
       <c r="D103" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E103" t="s">
-        <v>356</v>
+        <v>299</v>
       </c>
       <c r="F103" t="s">
-        <v>357</v>
+        <v>415</v>
       </c>
       <c r="G103">
         <v>59616498</v>
@@ -4807,25 +4823,25 @@
         <v>232</v>
       </c>
       <c r="B104" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C104" t="s">
-        <v>358</v>
+        <v>168</v>
       </c>
       <c r="D104" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E104" t="s">
-        <v>356</v>
+        <v>299</v>
       </c>
       <c r="F104" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
       <c r="G104">
         <v>31357953</v>
       </c>
       <c r="H104" t="s">
-        <v>360</v>
+        <v>472</v>
       </c>
       <c r="J104">
         <v>25</v>
@@ -4839,25 +4855,25 @@
         <v>233</v>
       </c>
       <c r="B105" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>361</v>
+        <v>169</v>
       </c>
       <c r="D105" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E105" t="s">
-        <v>356</v>
+        <v>299</v>
       </c>
       <c r="F105" t="s">
-        <v>362</v>
+        <v>417</v>
       </c>
       <c r="G105" t="s">
-        <v>363</v>
+        <v>459</v>
       </c>
       <c r="H105" t="s">
-        <v>364</v>
+        <v>473</v>
       </c>
       <c r="J105">
         <v>25</v>
@@ -4871,25 +4887,25 @@
         <v>234</v>
       </c>
       <c r="B106" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C106" t="s">
-        <v>365</v>
+        <v>170</v>
       </c>
       <c r="D106" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E106" t="s">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="F106" t="s">
-        <v>366</v>
+        <v>418</v>
       </c>
       <c r="G106">
         <v>47050351</v>
       </c>
       <c r="H106" t="s">
-        <v>367</v>
+        <v>474</v>
       </c>
       <c r="J106">
         <v>25</v>
@@ -4903,25 +4919,25 @@
         <v>235</v>
       </c>
       <c r="B107" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C107" t="s">
-        <v>368</v>
+        <v>171</v>
       </c>
       <c r="D107" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E107" t="s">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="F107" t="s">
-        <v>369</v>
+        <v>419</v>
       </c>
       <c r="G107">
         <v>56376500</v>
       </c>
       <c r="H107" t="s">
-        <v>370</v>
+        <v>475</v>
       </c>
       <c r="J107">
         <v>25</v>
@@ -4935,25 +4951,25 @@
         <v>236</v>
       </c>
       <c r="B108" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C108" t="s">
-        <v>371</v>
+        <v>172</v>
       </c>
       <c r="D108" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E108" t="s">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="F108" t="s">
-        <v>373</v>
+        <v>420</v>
       </c>
       <c r="G108">
         <v>53009229</v>
       </c>
       <c r="H108" t="s">
-        <v>374</v>
+        <v>476</v>
       </c>
       <c r="J108">
         <v>25</v>
@@ -4967,25 +4983,25 @@
         <v>237</v>
       </c>
       <c r="B109" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C109" t="s">
-        <v>375</v>
+        <v>173</v>
       </c>
       <c r="D109" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E109" t="s">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="F109" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="G109">
         <v>30308037</v>
       </c>
       <c r="H109" t="s">
-        <v>377</v>
+        <v>477</v>
       </c>
       <c r="J109">
         <v>25</v>
@@ -4999,25 +5015,25 @@
         <v>238</v>
       </c>
       <c r="B110" t="s">
-        <v>378</v>
+        <v>57</v>
       </c>
       <c r="C110" t="s">
-        <v>379</v>
+        <v>174</v>
       </c>
       <c r="D110" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E110" t="s">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="F110" t="s">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="G110">
         <v>59444640</v>
       </c>
       <c r="H110" t="s">
-        <v>381</v>
+        <v>478</v>
       </c>
       <c r="J110">
         <v>24</v>
@@ -5031,25 +5047,25 @@
         <v>239</v>
       </c>
       <c r="B111" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C111" t="s">
-        <v>382</v>
+        <v>175</v>
       </c>
       <c r="D111" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E111" t="s">
-        <v>383</v>
+        <v>301</v>
       </c>
       <c r="F111" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="G111">
         <v>38076396</v>
       </c>
       <c r="H111" t="s">
-        <v>385</v>
+        <v>479</v>
       </c>
       <c r="J111">
         <v>25</v>
@@ -5063,25 +5079,25 @@
         <v>240</v>
       </c>
       <c r="B112" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C112" t="s">
-        <v>386</v>
+        <v>176</v>
       </c>
       <c r="D112" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E112" t="s">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="F112" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="G112">
         <v>59934015</v>
       </c>
       <c r="H112" t="s">
-        <v>389</v>
+        <v>480</v>
       </c>
       <c r="J112">
         <v>50</v>
@@ -5095,25 +5111,25 @@
         <v>241</v>
       </c>
       <c r="B113" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C113" t="s">
-        <v>390</v>
+        <v>177</v>
       </c>
       <c r="D113" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E113" t="s">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="F113" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="G113">
         <v>46782645</v>
       </c>
       <c r="H113" t="s">
-        <v>392</v>
+        <v>481</v>
       </c>
       <c r="J113">
         <v>25</v>
@@ -5127,25 +5143,25 @@
         <v>242</v>
       </c>
       <c r="B114" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C114" t="s">
-        <v>393</v>
+        <v>178</v>
       </c>
       <c r="D114" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E114" t="s">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="F114" t="s">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="G114">
         <v>40407799</v>
       </c>
       <c r="H114" t="s">
-        <v>395</v>
+        <v>482</v>
       </c>
       <c r="J114">
         <v>25</v>
@@ -5159,25 +5175,25 @@
         <v>243</v>
       </c>
       <c r="B115" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C115" t="s">
-        <v>396</v>
+        <v>179</v>
       </c>
       <c r="D115" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E115" t="s">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="F115" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="G115" t="s">
-        <v>398</v>
+        <v>460</v>
       </c>
       <c r="H115" t="s">
-        <v>399</v>
+        <v>483</v>
       </c>
       <c r="J115">
         <v>25</v>
@@ -5191,25 +5207,25 @@
         <v>244</v>
       </c>
       <c r="B116" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C116" t="s">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="D116" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E116" t="s">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="F116" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="G116">
         <v>46748901</v>
       </c>
       <c r="H116" t="s">
-        <v>402</v>
+        <v>484</v>
       </c>
       <c r="J116">
         <v>25</v>
@@ -5223,25 +5239,25 @@
         <v>245</v>
       </c>
       <c r="B117" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C117" t="s">
-        <v>403</v>
+        <v>181</v>
       </c>
       <c r="D117" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E117" t="s">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="F117" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="G117">
         <v>32053375</v>
       </c>
       <c r="H117" t="s">
-        <v>405</v>
+        <v>485</v>
       </c>
       <c r="J117">
         <v>25</v>
@@ -5255,25 +5271,25 @@
         <v>246</v>
       </c>
       <c r="B118" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C118" t="s">
-        <v>406</v>
+        <v>182</v>
       </c>
       <c r="D118" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E118" t="s">
-        <v>407</v>
+        <v>303</v>
       </c>
       <c r="F118" t="s">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="G118">
         <v>58925475</v>
       </c>
       <c r="H118" t="s">
-        <v>408</v>
+        <v>486</v>
       </c>
       <c r="J118">
         <v>25</v>
@@ -5287,25 +5303,25 @@
         <v>247</v>
       </c>
       <c r="B119" t="s">
-        <v>409</v>
+        <v>58</v>
       </c>
       <c r="C119" t="s">
-        <v>410</v>
+        <v>183</v>
       </c>
       <c r="D119" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="E119" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="F119" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="G119">
         <v>79420425</v>
       </c>
       <c r="H119" t="s">
-        <v>412</v>
+        <v>487</v>
       </c>
       <c r="J119">
         <v>25</v>
@@ -5319,25 +5335,25 @@
         <v>248</v>
       </c>
       <c r="B120" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C120" t="s">
-        <v>413</v>
+        <v>184</v>
       </c>
       <c r="D120" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="E120" t="s">
-        <v>414</v>
+        <v>304</v>
       </c>
       <c r="F120" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="G120">
         <v>30194721</v>
       </c>
       <c r="H120" t="s">
-        <v>416</v>
+        <v>488</v>
       </c>
       <c r="J120">
         <v>25</v>
@@ -5351,25 +5367,25 @@
         <v>249</v>
       </c>
       <c r="B121" t="s">
-        <v>417</v>
+        <v>59</v>
       </c>
       <c r="C121" t="s">
-        <v>418</v>
+        <v>185</v>
       </c>
       <c r="D121" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="E121" t="s">
-        <v>419</v>
+        <v>538</v>
       </c>
       <c r="F121" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="G121">
         <v>79465395</v>
       </c>
       <c r="H121" t="s">
-        <v>421</v>
+        <v>489</v>
       </c>
       <c r="J121">
         <v>50</v>
@@ -5383,22 +5399,22 @@
         <v>250</v>
       </c>
       <c r="B122" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C122" t="s">
-        <v>422</v>
+        <v>186</v>
       </c>
       <c r="D122" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="E122" t="s">
-        <v>423</v>
+        <v>305</v>
       </c>
       <c r="F122" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="H122" t="s">
-        <v>425</v>
+        <v>490</v>
       </c>
       <c r="J122">
         <v>50</v>
@@ -5412,25 +5428,25 @@
         <v>251</v>
       </c>
       <c r="B123" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C123" t="s">
-        <v>426</v>
+        <v>187</v>
       </c>
       <c r="D123" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="E123" t="s">
-        <v>427</v>
+        <v>306</v>
       </c>
       <c r="F123" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="G123">
         <v>40102428</v>
       </c>
       <c r="H123" t="s">
-        <v>429</v>
+        <v>491</v>
       </c>
       <c r="J123">
         <v>25</v>
@@ -5444,25 +5460,25 @@
         <v>252</v>
       </c>
       <c r="B124" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C124" t="s">
-        <v>430</v>
+        <v>188</v>
       </c>
       <c r="D124" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="E124" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="F124" t="s">
-        <v>540</v>
+        <v>435</v>
       </c>
       <c r="G124">
         <v>40124127</v>
       </c>
       <c r="H124" t="s">
-        <v>431</v>
+        <v>492</v>
       </c>
       <c r="J124">
         <v>25</v>
@@ -5476,25 +5492,25 @@
         <v>253</v>
       </c>
       <c r="B125" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C125" t="s">
-        <v>432</v>
+        <v>189</v>
       </c>
       <c r="D125" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="E125" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="F125" t="s">
-        <v>540</v>
+        <v>435</v>
       </c>
       <c r="G125">
         <v>40124127</v>
       </c>
       <c r="H125" t="s">
-        <v>431</v>
+        <v>492</v>
       </c>
       <c r="J125">
         <v>25</v>
@@ -5508,25 +5524,25 @@
         <v>254</v>
       </c>
       <c r="B126" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C126" t="s">
-        <v>433</v>
+        <v>190</v>
       </c>
       <c r="D126" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="E126" t="s">
-        <v>434</v>
+        <v>307</v>
       </c>
       <c r="F126" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G126" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="H126" t="s">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="J126">
         <v>25</v>
@@ -5540,25 +5556,25 @@
         <v>255</v>
       </c>
       <c r="B127" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C127" t="s">
-        <v>438</v>
+        <v>191</v>
       </c>
       <c r="D127" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="E127" t="s">
-        <v>439</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="G127">
         <v>31103174</v>
       </c>
       <c r="H127" t="s">
-        <v>441</v>
+        <v>494</v>
       </c>
       <c r="J127">
         <v>25</v>
@@ -5572,25 +5588,25 @@
         <v>256</v>
       </c>
       <c r="B128" t="s">
-        <v>442</v>
+        <v>60</v>
       </c>
       <c r="C128" t="s">
-        <v>443</v>
+        <v>192</v>
       </c>
       <c r="D128" t="s">
-        <v>444</v>
+        <v>231</v>
       </c>
       <c r="E128" t="s">
-        <v>444</v>
+        <v>231</v>
       </c>
       <c r="F128" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="G128">
         <v>40645842</v>
       </c>
       <c r="H128" t="s">
-        <v>446</v>
+        <v>495</v>
       </c>
       <c r="J128">
         <v>25</v>
@@ -5604,25 +5620,25 @@
         <v>257</v>
       </c>
       <c r="B129" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C129" t="s">
-        <v>447</v>
+        <v>193</v>
       </c>
       <c r="D129" t="s">
-        <v>444</v>
+        <v>231</v>
       </c>
       <c r="E129" t="s">
-        <v>444</v>
+        <v>231</v>
       </c>
       <c r="F129" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="G129" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="H129" t="s">
-        <v>450</v>
+        <v>496</v>
       </c>
       <c r="J129">
         <v>25</v>
@@ -5636,25 +5652,25 @@
         <v>258</v>
       </c>
       <c r="B130" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C130" t="s">
-        <v>451</v>
+        <v>194</v>
       </c>
       <c r="D130" t="s">
-        <v>444</v>
+        <v>231</v>
       </c>
       <c r="E130" t="s">
-        <v>452</v>
+        <v>309</v>
       </c>
       <c r="F130" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="G130">
         <v>57775944</v>
       </c>
       <c r="H130" t="s">
-        <v>454</v>
+        <v>497</v>
       </c>
       <c r="J130">
         <v>25</v>
@@ -5668,25 +5684,25 @@
         <v>259</v>
       </c>
       <c r="B131" t="s">
+        <v>54</v>
+      </c>
+      <c r="C131" t="s">
+        <v>195</v>
+      </c>
+      <c r="D131" t="s">
+        <v>231</v>
+      </c>
+      <c r="E131" t="s">
         <v>310</v>
       </c>
-      <c r="C131" t="s">
-        <v>455</v>
-      </c>
-      <c r="D131" t="s">
-        <v>444</v>
-      </c>
-      <c r="E131" t="s">
-        <v>456</v>
-      </c>
       <c r="F131" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="G131">
         <v>79247161</v>
       </c>
       <c r="H131" t="s">
-        <v>458</v>
+        <v>498</v>
       </c>
       <c r="J131">
         <v>25</v>
@@ -5700,25 +5716,25 @@
         <v>260</v>
       </c>
       <c r="B132" t="s">
-        <v>459</v>
+        <v>61</v>
       </c>
       <c r="C132" t="s">
-        <v>460</v>
+        <v>196</v>
       </c>
       <c r="D132" t="s">
-        <v>444</v>
+        <v>231</v>
       </c>
       <c r="E132" t="s">
-        <v>456</v>
+        <v>310</v>
       </c>
       <c r="F132" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="G132">
         <v>46354246</v>
       </c>
       <c r="H132" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="J132">
         <v>25</v>
@@ -5732,25 +5748,25 @@
         <v>261</v>
       </c>
       <c r="B133" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C133" t="s">
-        <v>463</v>
+        <v>197</v>
       </c>
       <c r="D133" t="s">
-        <v>444</v>
+        <v>231</v>
       </c>
       <c r="E133" t="s">
-        <v>464</v>
+        <v>311</v>
       </c>
       <c r="F133" t="s">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="G133">
         <v>31254619</v>
       </c>
       <c r="H133" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="J133">
         <v>25</v>
@@ -5764,25 +5780,25 @@
         <v>262</v>
       </c>
       <c r="B134" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C134" t="s">
-        <v>467</v>
+        <v>198</v>
       </c>
       <c r="D134" t="s">
+        <v>231</v>
+      </c>
+      <c r="E134" t="s">
+        <v>312</v>
+      </c>
+      <c r="F134" t="s">
         <v>444</v>
-      </c>
-      <c r="E134" t="s">
-        <v>468</v>
-      </c>
-      <c r="F134" t="s">
-        <v>469</v>
       </c>
       <c r="G134">
         <v>30441503</v>
       </c>
       <c r="H134" t="s">
-        <v>470</v>
+        <v>501</v>
       </c>
       <c r="J134">
         <v>25</v>
@@ -5796,25 +5812,25 @@
         <v>263</v>
       </c>
       <c r="B135" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C135" t="s">
-        <v>471</v>
+        <v>199</v>
       </c>
       <c r="D135" t="s">
+        <v>231</v>
+      </c>
+      <c r="E135" t="s">
+        <v>312</v>
+      </c>
+      <c r="F135" t="s">
         <v>444</v>
-      </c>
-      <c r="E135" t="s">
-        <v>468</v>
-      </c>
-      <c r="F135" t="s">
-        <v>469</v>
       </c>
       <c r="G135">
         <v>30441503</v>
       </c>
       <c r="H135" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="J135">
         <v>25</v>
@@ -5828,25 +5844,25 @@
         <v>264</v>
       </c>
       <c r="B136" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C136" t="s">
-        <v>473</v>
+        <v>200</v>
       </c>
       <c r="D136" t="s">
-        <v>444</v>
+        <v>231</v>
       </c>
       <c r="E136" t="s">
-        <v>474</v>
+        <v>313</v>
       </c>
       <c r="F136" t="s">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="G136">
         <v>59091890</v>
       </c>
       <c r="H136" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="J136">
         <v>25</v>
@@ -5860,25 +5876,25 @@
         <v>265</v>
       </c>
       <c r="B137" t="s">
-        <v>477</v>
+        <v>62</v>
       </c>
       <c r="C137" t="s">
-        <v>478</v>
+        <v>201</v>
       </c>
       <c r="D137" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="E137" t="s">
-        <v>479</v>
+        <v>314</v>
       </c>
       <c r="F137" t="s">
-        <v>480</v>
+        <v>446</v>
       </c>
       <c r="G137">
         <v>40101472</v>
       </c>
       <c r="H137" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="J137">
         <v>25</v>
@@ -5892,25 +5908,25 @@
         <v>266</v>
       </c>
       <c r="B138" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C138" t="s">
-        <v>482</v>
+        <v>202</v>
       </c>
       <c r="D138" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="E138" t="s">
-        <v>483</v>
+        <v>315</v>
       </c>
       <c r="F138" t="s">
-        <v>328</v>
+        <v>408</v>
       </c>
       <c r="G138">
         <v>46572036</v>
       </c>
       <c r="H138" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="J138">
         <v>25</v>
@@ -5924,25 +5940,25 @@
         <v>267</v>
       </c>
       <c r="B139" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C139" t="s">
-        <v>485</v>
+        <v>203</v>
       </c>
       <c r="D139" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="E139" t="s">
-        <v>486</v>
+        <v>316</v>
       </c>
       <c r="F139" t="s">
-        <v>487</v>
+        <v>447</v>
       </c>
       <c r="G139">
         <v>49420095</v>
       </c>
       <c r="H139" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="J139">
         <v>25</v>
@@ -5956,25 +5972,25 @@
         <v>268</v>
       </c>
       <c r="B140" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C140" t="s">
-        <v>489</v>
+        <v>204</v>
       </c>
       <c r="D140" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="E140" t="s">
-        <v>490</v>
+        <v>539</v>
       </c>
       <c r="F140" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="G140">
         <v>49006911</v>
       </c>
       <c r="H140" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="J140">
         <v>25</v>
@@ -5988,25 +6004,25 @@
         <v>269</v>
       </c>
       <c r="B141" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C141" t="s">
-        <v>493</v>
+        <v>205</v>
       </c>
       <c r="D141" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="E141" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="F141" t="s">
-        <v>494</v>
+        <v>449</v>
       </c>
       <c r="G141">
         <v>77554630</v>
       </c>
       <c r="H141" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="J141">
         <v>25</v>
@@ -6020,25 +6036,25 @@
         <v>270</v>
       </c>
       <c r="B142" t="s">
-        <v>496</v>
+        <v>63</v>
       </c>
       <c r="C142" t="s">
-        <v>497</v>
+        <v>206</v>
       </c>
       <c r="D142" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="E142" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="F142" t="s">
-        <v>498</v>
+        <v>450</v>
       </c>
       <c r="G142">
         <v>46547266</v>
       </c>
       <c r="H142" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="J142">
         <v>25</v>
@@ -6052,25 +6068,25 @@
         <v>271</v>
       </c>
       <c r="B143" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="C143" t="s">
-        <v>500</v>
+        <v>207</v>
       </c>
       <c r="D143" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="E143" t="s">
-        <v>541</v>
+        <v>317</v>
       </c>
       <c r="F143" t="s">
-        <v>501</v>
+        <v>451</v>
       </c>
       <c r="G143">
         <v>42446716</v>
       </c>
       <c r="H143" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="J143">
         <v>25</v>
@@ -6084,28 +6100,28 @@
         <v>272</v>
       </c>
       <c r="B144" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C144" t="s">
-        <v>503</v>
+        <v>208</v>
       </c>
       <c r="D144" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E144" t="s">
+        <v>303</v>
+      </c>
+      <c r="F144" t="s">
         <v>407</v>
-      </c>
-      <c r="F144" t="s">
-        <v>324</v>
       </c>
       <c r="G144">
         <v>58925475</v>
       </c>
       <c r="H144" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="I144" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="J144">
         <v>25</v>
@@ -6119,28 +6135,28 @@
         <v>273</v>
       </c>
       <c r="B145" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C145" t="s">
-        <v>368</v>
+        <v>171</v>
       </c>
       <c r="D145" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E145" t="s">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="F145" t="s">
-        <v>369</v>
+        <v>419</v>
       </c>
       <c r="G145">
         <v>56376500</v>
       </c>
       <c r="H145" t="s">
-        <v>370</v>
+        <v>475</v>
       </c>
       <c r="I145" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="J145">
         <v>25</v>
@@ -6154,28 +6170,28 @@
         <v>274</v>
       </c>
       <c r="B146" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C146" t="s">
-        <v>403</v>
+        <v>181</v>
       </c>
       <c r="D146" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E146" t="s">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="F146" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="G146">
         <v>32053375</v>
       </c>
       <c r="H146" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="I146" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="J146">
         <v>25</v>
@@ -6189,28 +6205,28 @@
         <v>275</v>
       </c>
       <c r="B147" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C147" t="s">
-        <v>382</v>
+        <v>175</v>
       </c>
       <c r="D147" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E147" t="s">
-        <v>509</v>
+        <v>301</v>
       </c>
       <c r="F147" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="G147">
         <v>38076396</v>
       </c>
       <c r="H147" t="s">
-        <v>385</v>
+        <v>479</v>
       </c>
       <c r="I147" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="J147">
         <v>25</v>
@@ -6224,28 +6240,28 @@
         <v>276</v>
       </c>
       <c r="B148" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C148" t="s">
-        <v>390</v>
+        <v>177</v>
       </c>
       <c r="D148" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E148" t="s">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="F148" t="s">
-        <v>304</v>
+        <v>401</v>
       </c>
       <c r="G148">
         <v>46782645</v>
       </c>
       <c r="H148" t="s">
-        <v>392</v>
+        <v>481</v>
       </c>
       <c r="I148" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="J148">
         <v>25</v>
@@ -6259,28 +6275,28 @@
         <v>277</v>
       </c>
       <c r="B149" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C149" t="s">
-        <v>365</v>
+        <v>170</v>
       </c>
       <c r="D149" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E149" t="s">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="F149" t="s">
-        <v>512</v>
+        <v>452</v>
       </c>
       <c r="G149">
         <v>47050351</v>
       </c>
       <c r="H149" t="s">
-        <v>367</v>
+        <v>474</v>
       </c>
       <c r="I149" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="J149">
         <v>25</v>
@@ -6294,28 +6310,28 @@
         <v>278</v>
       </c>
       <c r="B150" t="s">
-        <v>378</v>
+        <v>57</v>
       </c>
       <c r="C150" t="s">
-        <v>379</v>
+        <v>174</v>
       </c>
       <c r="D150" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E150" t="s">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="F150" t="s">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="G150">
         <v>59444640</v>
       </c>
       <c r="H150" t="s">
-        <v>381</v>
+        <v>478</v>
       </c>
       <c r="I150" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="J150">
         <v>25</v>
@@ -6329,28 +6345,28 @@
         <v>279</v>
       </c>
       <c r="B151" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C151" t="s">
-        <v>371</v>
+        <v>172</v>
       </c>
       <c r="D151" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E151" t="s">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="F151" t="s">
-        <v>515</v>
+        <v>453</v>
       </c>
       <c r="G151">
         <v>53009229</v>
       </c>
       <c r="H151" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="I151" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="J151">
         <v>25</v>
@@ -6364,28 +6380,28 @@
         <v>280</v>
       </c>
       <c r="B152" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C152" t="s">
-        <v>375</v>
+        <v>173</v>
       </c>
       <c r="D152" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E152" t="s">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="F152" t="s">
-        <v>518</v>
+        <v>454</v>
       </c>
       <c r="G152">
         <v>30308087</v>
       </c>
       <c r="H152" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="I152" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="J152">
         <v>25</v>
@@ -6399,28 +6415,28 @@
         <v>281</v>
       </c>
       <c r="B153" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C153" t="s">
-        <v>386</v>
+        <v>176</v>
       </c>
       <c r="D153" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E153" t="s">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="F153" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="G153">
         <v>59934015</v>
       </c>
       <c r="H153" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="I153" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="J153">
         <v>50</v>
@@ -6434,28 +6450,28 @@
         <v>282</v>
       </c>
       <c r="B154" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C154" t="s">
-        <v>393</v>
+        <v>178</v>
       </c>
       <c r="D154" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E154" t="s">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="F154" t="s">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="G154">
         <v>40407799</v>
       </c>
       <c r="H154" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="I154" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="J154">
         <v>25</v>
@@ -6469,28 +6485,28 @@
         <v>283</v>
       </c>
       <c r="B155" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C155" t="s">
-        <v>355</v>
+        <v>167</v>
       </c>
       <c r="D155" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="E155" t="s">
-        <v>356</v>
+        <v>299</v>
       </c>
       <c r="F155" t="s">
-        <v>357</v>
+        <v>415</v>
       </c>
       <c r="G155">
         <v>51341841</v>
       </c>
       <c r="H155" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="I155" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="J155">
         <v>25</v>
@@ -6504,28 +6520,28 @@
         <v>284</v>
       </c>
       <c r="B156" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C156" t="s">
-        <v>332</v>
+        <v>160</v>
       </c>
       <c r="D156" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E156" t="s">
-        <v>333</v>
+        <v>295</v>
       </c>
       <c r="F156" t="s">
-        <v>334</v>
+        <v>409</v>
       </c>
       <c r="G156">
         <v>49179398</v>
       </c>
       <c r="H156" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="I156" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="J156">
         <v>25</v>
@@ -6539,28 +6555,28 @@
         <v>285</v>
       </c>
       <c r="B157" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C157" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
       <c r="D157" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E157" t="s">
-        <v>350</v>
+        <v>297</v>
       </c>
       <c r="F157" t="s">
-        <v>351</v>
+        <v>413</v>
       </c>
       <c r="G157">
         <v>57767683</v>
       </c>
       <c r="H157" t="s">
-        <v>352</v>
+        <v>471</v>
       </c>
       <c r="I157" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="J157">
         <v>25</v>
@@ -6574,28 +6590,28 @@
         <v>286</v>
       </c>
       <c r="B158" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C158" t="s">
-        <v>314</v>
+        <v>156</v>
       </c>
       <c r="D158" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E158" t="s">
-        <v>193</v>
+        <v>266</v>
       </c>
       <c r="F158" t="s">
-        <v>530</v>
+        <v>455</v>
       </c>
       <c r="G158">
         <v>53174572</v>
       </c>
       <c r="H158" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="I158" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J158">
         <v>25</v>
@@ -6609,25 +6625,25 @@
         <v>287</v>
       </c>
       <c r="B159" t="s">
-        <v>533</v>
+        <v>64</v>
       </c>
       <c r="C159" t="s">
-        <v>348</v>
+        <v>164</v>
       </c>
       <c r="D159" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E159" t="s">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="F159" t="s">
-        <v>534</v>
+        <v>456</v>
       </c>
       <c r="G159">
         <v>40303909</v>
       </c>
       <c r="H159" t="s">
-        <v>347</v>
+        <v>470</v>
       </c>
       <c r="I159" t="s">
         <v>535</v>
@@ -6644,25 +6660,25 @@
         <v>288</v>
       </c>
       <c r="B160" t="s">
-        <v>536</v>
+        <v>65</v>
       </c>
       <c r="C160" t="s">
-        <v>345</v>
+        <v>163</v>
       </c>
       <c r="D160" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E160" t="s">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="F160" t="s">
-        <v>534</v>
+        <v>456</v>
       </c>
       <c r="G160">
         <v>40303909</v>
       </c>
       <c r="H160" t="s">
-        <v>347</v>
+        <v>470</v>
       </c>
       <c r="I160" t="s">
         <v>535</v>
@@ -6679,28 +6695,28 @@
         <v>289</v>
       </c>
       <c r="B161" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C161" t="s">
-        <v>317</v>
+        <v>157</v>
       </c>
       <c r="D161" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E161" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="F161" t="s">
-        <v>319</v>
+        <v>406</v>
       </c>
       <c r="G161">
         <v>49823719</v>
       </c>
       <c r="H161" t="s">
-        <v>321</v>
+        <v>464</v>
       </c>
       <c r="I161" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="J161">
         <v>25</v>
@@ -6714,28 +6730,28 @@
         <v>290</v>
       </c>
       <c r="B162" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C162" t="s">
-        <v>340</v>
+        <v>162</v>
       </c>
       <c r="D162" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E162" t="s">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="F162" t="s">
-        <v>342</v>
+        <v>411</v>
       </c>
       <c r="G162">
         <v>55245770</v>
       </c>
       <c r="H162" t="s">
-        <v>343</v>
+        <v>469</v>
       </c>
       <c r="I162" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J162">
         <v>25</v>
@@ -6745,7 +6761,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>